--- a/full_results.xlsx
+++ b/full_results.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\RCMP\speech_recognition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F783B33-A4BF-4DFB-8A7A-FB3828FA7721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E88A9B-85E8-4D04-93AB-70D25E037B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-9285" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9285" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="whisper-base" sheetId="1" r:id="rId1"/>
     <sheet name="whisper-large-v3" sheetId="2" r:id="rId2"/>
-    <sheet name="comparison" sheetId="3" r:id="rId3"/>
+    <sheet name="wav2vec2_arabic" sheetId="4" r:id="rId3"/>
+    <sheet name="comparison" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="690">
   <si>
     <t>audio_path</t>
   </si>
@@ -1795,10 +1796,316 @@
     <t>Accurcay (# of predictions over 75% / very similar threshold)</t>
   </si>
   <si>
-    <t>other model?</t>
-  </si>
-  <si>
-    <t>?</t>
+    <t>ألديك قلم</t>
+  </si>
+  <si>
+    <t>أين المشكل</t>
+  </si>
+  <si>
+    <t>إنك تتكلم ك أمك</t>
+  </si>
+  <si>
+    <t>تاكوم هم بذتك هكة نا جبابي</t>
+  </si>
+  <si>
+    <t>takum hum badhak na jababi</t>
+  </si>
+  <si>
+    <t>لا أستطيع أن أجد أي خطئ في نظريته</t>
+  </si>
+  <si>
+    <t>هل ستسافر إلى أمريكا الشهر القادم</t>
+  </si>
+  <si>
+    <t>إنه أتبكي</t>
+  </si>
+  <si>
+    <t>he is crying</t>
+  </si>
+  <si>
+    <t>كم الساعة</t>
+  </si>
+  <si>
+    <t>what's the time</t>
+  </si>
+  <si>
+    <t>سمعت اليوم شيئا جديدا</t>
+  </si>
+  <si>
+    <t>الرزل الطويل خرج من البيت</t>
+  </si>
+  <si>
+    <t>لا تتدخر</t>
+  </si>
+  <si>
+    <t>don't be stingy</t>
+  </si>
+  <si>
+    <t>لماذا تتجاهل ما أقوله</t>
+  </si>
+  <si>
+    <t>إنني استمع إلى المدايعة</t>
+  </si>
+  <si>
+    <t>i am listening to the cacophony</t>
+  </si>
+  <si>
+    <t>أنا متعب أعتقد أنني سأخلد إلى السرير</t>
+  </si>
+  <si>
+    <t>أنا متعب أعتخدأ لسأخضل إلى السرير</t>
+  </si>
+  <si>
+    <t>i'm tired i'm going to bed</t>
+  </si>
+  <si>
+    <t>الكرز احمر</t>
+  </si>
+  <si>
+    <t>red cherries</t>
+  </si>
+  <si>
+    <t>ندوج كل يوم تقريبا</t>
+  </si>
+  <si>
+    <t>we go almost every day</t>
+  </si>
+  <si>
+    <t>خزن العميق لا يسعب الكلمات</t>
+  </si>
+  <si>
+    <t>the deep storehouse is beyond words</t>
+  </si>
+  <si>
+    <t>القفل لا يوم شي بعده</t>
+  </si>
+  <si>
+    <t>lock up no day after it</t>
+  </si>
+  <si>
+    <t>أيمكنني ل نطرح بعد الأسئنة</t>
+  </si>
+  <si>
+    <t>can i ask some more questions?</t>
+  </si>
+  <si>
+    <t>ألم شنبر</t>
+  </si>
+  <si>
+    <t>shanbar pain</t>
+  </si>
+  <si>
+    <t>أشترية سعة</t>
+  </si>
+  <si>
+    <t>i buy capacity</t>
+  </si>
+  <si>
+    <t>هتاني أختاني</t>
+  </si>
+  <si>
+    <t>this is my sister</t>
+  </si>
+  <si>
+    <t>إنهُ حالي في رحلة عمل في نعجويا</t>
+  </si>
+  <si>
+    <t>i am currently on a business trip in najoua.</t>
+  </si>
+  <si>
+    <t>ما قلته ليس له أي مارا</t>
+  </si>
+  <si>
+    <t>what i said has no meaning.</t>
+  </si>
+  <si>
+    <t>عما تبحس</t>
+  </si>
+  <si>
+    <t>الأمل ليس استرتيجية</t>
+  </si>
+  <si>
+    <t>لا لن تحتعته</t>
+  </si>
+  <si>
+    <t>no, you won't.</t>
+  </si>
+  <si>
+    <t>كلّ ما يحصل يحصل لسابن</t>
+  </si>
+  <si>
+    <t>whatever happens happens to sabin.</t>
+  </si>
+  <si>
+    <t>كيف حال الطقس</t>
+  </si>
+  <si>
+    <t>بعض أصدقائي يمكنهم تحدث الإنجليزية جيدا</t>
+  </si>
+  <si>
+    <t>في البداية وجه سعوة في التقل معبيته جديد</t>
+  </si>
+  <si>
+    <t>at first, the face of sa'wa in the tradition is filled with new</t>
+  </si>
+  <si>
+    <t>بل لذهى أن تعاود الإتصار بي من فضلك</t>
+  </si>
+  <si>
+    <t>rather, it is my pleasure to win over me again, please.</t>
+  </si>
+  <si>
+    <t>بيتك أكبر من بيتي ثلاث مراء</t>
+  </si>
+  <si>
+    <t>كان ذاك أرنوبا شريراً</t>
+  </si>
+  <si>
+    <t>تعال وأصبح معيض</t>
+  </si>
+  <si>
+    <t>come and become a supporter</t>
+  </si>
+  <si>
+    <t>كان هناك حوال عشرين دولارا</t>
+  </si>
+  <si>
+    <t>بالكادي أستطيع سمعك</t>
+  </si>
+  <si>
+    <t>i can barely hear you</t>
+  </si>
+  <si>
+    <t>كان أي شيء غير عادي غوير طبيل كاثيًا لإرسال زمين  إلى ملوكايف</t>
+  </si>
+  <si>
+    <t>anything unusual would have sent a troll to moluccas.</t>
+  </si>
+  <si>
+    <t>يتحدث مايك اليابانين جيداً</t>
+  </si>
+  <si>
+    <t>غطاه الوحل من رأسه إلى أخمص قدمه</t>
+  </si>
+  <si>
+    <t>التحدث بالإنجليزية ليس أمراً سعلً</t>
+  </si>
+  <si>
+    <t>speaking english is not a cough</t>
+  </si>
+  <si>
+    <t>بعض أصدقائي يمكنما  تحدث الإنجليزية جيداً</t>
+  </si>
+  <si>
+    <t>طعها في أي مكان تشاء</t>
+  </si>
+  <si>
+    <t>eat it anywhere you want</t>
+  </si>
+  <si>
+    <t>دعني أشرح سبب صولي متأخّراً</t>
+  </si>
+  <si>
+    <t>let me explain why i'm late.</t>
+  </si>
+  <si>
+    <t>في وقت واحد سيا تم إن شاء أشرات من دول الكمنورفي التعاونية</t>
+  </si>
+  <si>
+    <t>at the same time, signals from the commonwealth of independent states will be issued.</t>
+  </si>
+  <si>
+    <t>حملت ثلاثت كتب</t>
+  </si>
+  <si>
+    <t>وفقاً للشاعر إبريل هو أقسى شهر</t>
+  </si>
+  <si>
+    <t>يا لها من ذكرا</t>
+  </si>
+  <si>
+    <t>اتصل ابنها من ييويورك</t>
+  </si>
+  <si>
+    <t>يعم الأب في مصنح</t>
+  </si>
+  <si>
+    <t>father works in a factory</t>
+  </si>
+  <si>
+    <t>ربملأ</t>
+  </si>
+  <si>
+    <t>maybe i will fill it</t>
+  </si>
+  <si>
+    <t>أنا أرقت</t>
+  </si>
+  <si>
+    <t>i have insomnia</t>
+  </si>
+  <si>
+    <t>ملأت كيسها بالطفاح</t>
+  </si>
+  <si>
+    <t>she filled her bag with scum.</t>
+  </si>
+  <si>
+    <t>أهلاً هل تعمل هنا</t>
+  </si>
+  <si>
+    <t>أعمل كل يوم ما عد يوم الأحد</t>
+  </si>
+  <si>
+    <t>اتَّفَقُوا عَلَى انْتِخَى بِهِ رَئِيسًا</t>
+  </si>
+  <si>
+    <t>they agreed to elect him as president.</t>
+  </si>
+  <si>
+    <t>نجحنا كلّنا في الإمتحان</t>
+  </si>
+  <si>
+    <t>لا أذكُرُ رحن تلك الأغْنِية</t>
+  </si>
+  <si>
+    <t>i don't remember the spirit of that song</t>
+  </si>
+  <si>
+    <t>لَنْ يَكُونَ بِوِسْعِ الْقُدُومُ بِسَبَبِ مَرَبِهِ</t>
+  </si>
+  <si>
+    <t>he won't be able to come because of his trouble.</t>
+  </si>
+  <si>
+    <t>توقف الحاسوب عن العمل بعد تحديفٍ آلي للنظام</t>
+  </si>
+  <si>
+    <t>لم أقصد شيئاً</t>
+  </si>
+  <si>
+    <t>لم أقسد شيء</t>
+  </si>
+  <si>
+    <t>i didn't spoil anything</t>
+  </si>
+  <si>
+    <t>عزفت لحنا على البيانو</t>
+  </si>
+  <si>
+    <t>Trained on common voice dataset, kinda cheating...</t>
+  </si>
+  <si>
+    <t>WER_wav2vec2_arabic</t>
+  </si>
+  <si>
+    <t>semantic_sim_wav2vec2_arabic</t>
+  </si>
+  <si>
+    <t>semanticly_correct_wav2vec2_arabic</t>
+  </si>
+  <si>
+    <t>wav2vec2_arabic</t>
   </si>
 </sst>
 </file>
@@ -1827,12 +2134,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -1915,7 +2234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1930,10 +2249,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7519,25 +7842,2674 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEC63B6-936A-42DA-8D2C-7A1074DEA856}">
+  <dimension ref="A1:K101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="28.21875" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" customWidth="1"/>
+    <col min="11" max="11" width="52.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>0.99999994039535522</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>588</v>
+      </c>
+      <c r="E4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>589</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>590</v>
+      </c>
+      <c r="H5">
+        <v>4.1545651853084557E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>591</v>
+      </c>
+      <c r="E6">
+        <v>0.125</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>592</v>
+      </c>
+      <c r="E7">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>593</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>594</v>
+      </c>
+      <c r="H8">
+        <v>0.75318223237991333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9">
+        <v>0.99999994039535522</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>595</v>
+      </c>
+      <c r="E10">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" t="s">
+        <v>596</v>
+      </c>
+      <c r="H10">
+        <v>0.97012150287628174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>597</v>
+      </c>
+      <c r="E13">
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
+        <v>598</v>
+      </c>
+      <c r="E17">
+        <v>0.2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>599</v>
+      </c>
+      <c r="E18">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" t="s">
+        <v>600</v>
+      </c>
+      <c r="H18">
+        <v>0.32088717818260187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>601</v>
+      </c>
+      <c r="E19">
+        <v>0.2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19">
+        <v>0.99999994039535522</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>602</v>
+      </c>
+      <c r="E20">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" t="s">
+        <v>603</v>
+      </c>
+      <c r="H20">
+        <v>0.54973769187927246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>604</v>
+      </c>
+      <c r="D22" t="s">
+        <v>605</v>
+      </c>
+      <c r="E22">
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="F22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>606</v>
+      </c>
+      <c r="H22">
+        <v>0.90663361549377441</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s">
+        <v>607</v>
+      </c>
+      <c r="E23">
+        <v>0.5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" t="s">
+        <v>608</v>
+      </c>
+      <c r="H23">
+        <v>0.84008181095123291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24">
+        <v>0.9999997615814209</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" t="s">
+        <v>609</v>
+      </c>
+      <c r="E25">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" t="s">
+        <v>610</v>
+      </c>
+      <c r="H25">
+        <v>0.31205347180366522</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" t="s">
+        <v>611</v>
+      </c>
+      <c r="E27">
+        <v>0.4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" t="s">
+        <v>612</v>
+      </c>
+      <c r="H27">
+        <v>0.22744505107402799</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" t="s">
+        <v>613</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" t="s">
+        <v>614</v>
+      </c>
+      <c r="H28">
+        <v>5.7809960097074509E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" t="s">
+        <v>615</v>
+      </c>
+      <c r="E29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F29" t="s">
+        <v>141</v>
+      </c>
+      <c r="G29" t="s">
+        <v>616</v>
+      </c>
+      <c r="H29">
+        <v>0.82445734739303589</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>617</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>146</v>
+      </c>
+      <c r="G30" t="s">
+        <v>618</v>
+      </c>
+      <c r="H30">
+        <v>8.5401400923728943E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" t="s">
+        <v>619</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" t="s">
+        <v>620</v>
+      </c>
+      <c r="H31">
+        <v>0.3049854040145874</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32" t="s">
+        <v>155</v>
+      </c>
+      <c r="G32" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33" t="s">
+        <v>159</v>
+      </c>
+      <c r="G33" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" t="s">
+        <v>621</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>164</v>
+      </c>
+      <c r="G34" t="s">
+        <v>622</v>
+      </c>
+      <c r="H34">
+        <v>0.60369712114334106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" t="s">
+        <v>623</v>
+      </c>
+      <c r="E35">
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="F35" t="s">
+        <v>169</v>
+      </c>
+      <c r="G35" t="s">
+        <v>624</v>
+      </c>
+      <c r="H35">
+        <v>0.44888666272163391</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="s">
+        <v>174</v>
+      </c>
+      <c r="G36" t="s">
+        <v>174</v>
+      </c>
+      <c r="H36">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" t="s">
+        <v>625</v>
+      </c>
+      <c r="E37">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="F37" t="s">
+        <v>179</v>
+      </c>
+      <c r="G37" t="s">
+        <v>626</v>
+      </c>
+      <c r="H37">
+        <v>0.71904122829437256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" t="s">
+        <v>627</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>184</v>
+      </c>
+      <c r="G38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H38">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" t="s">
+        <v>628</v>
+      </c>
+      <c r="E39">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F39" t="s">
+        <v>189</v>
+      </c>
+      <c r="G39" t="s">
+        <v>189</v>
+      </c>
+      <c r="H39">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
+        <v>194</v>
+      </c>
+      <c r="G40" t="s">
+        <v>194</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" t="s">
+        <v>629</v>
+      </c>
+      <c r="E41">
+        <v>0.5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>199</v>
+      </c>
+      <c r="G41" t="s">
+        <v>630</v>
+      </c>
+      <c r="H41">
+        <v>0.43706187605857849</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="s">
+        <v>204</v>
+      </c>
+      <c r="G42" t="s">
+        <v>204</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="s">
+        <v>209</v>
+      </c>
+      <c r="G43" t="s">
+        <v>209</v>
+      </c>
+      <c r="H43">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" t="s">
+        <v>212</v>
+      </c>
+      <c r="D44" t="s">
+        <v>212</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>214</v>
+      </c>
+      <c r="G44" t="s">
+        <v>214</v>
+      </c>
+      <c r="H44">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" t="s">
+        <v>631</v>
+      </c>
+      <c r="E45">
+        <v>0.5</v>
+      </c>
+      <c r="F45" t="s">
+        <v>219</v>
+      </c>
+      <c r="G45" t="s">
+        <v>632</v>
+      </c>
+      <c r="H45">
+        <v>9.0471811592578888E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" t="s">
+        <v>633</v>
+      </c>
+      <c r="E46">
+        <v>0.25</v>
+      </c>
+      <c r="F46" t="s">
+        <v>224</v>
+      </c>
+      <c r="G46" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" t="s">
+        <v>227</v>
+      </c>
+      <c r="D47" t="s">
+        <v>634</v>
+      </c>
+      <c r="E47">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="F47" t="s">
+        <v>229</v>
+      </c>
+      <c r="G47" t="s">
+        <v>229</v>
+      </c>
+      <c r="H47">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>231</v>
+      </c>
+      <c r="C48" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>234</v>
+      </c>
+      <c r="G48" t="s">
+        <v>234</v>
+      </c>
+      <c r="H48">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" t="s">
+        <v>237</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="s">
+        <v>239</v>
+      </c>
+      <c r="G49" t="s">
+        <v>239</v>
+      </c>
+      <c r="H49">
+        <v>0.99999982118606567</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" t="s">
+        <v>242</v>
+      </c>
+      <c r="D50" t="s">
+        <v>635</v>
+      </c>
+      <c r="E50">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F50" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" t="s">
+        <v>636</v>
+      </c>
+      <c r="H50">
+        <v>0.19441559910774231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>246</v>
+      </c>
+      <c r="C51" t="s">
+        <v>247</v>
+      </c>
+      <c r="D51" t="s">
+        <v>637</v>
+      </c>
+      <c r="E51">
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="F51" t="s">
+        <v>249</v>
+      </c>
+      <c r="G51" t="s">
+        <v>638</v>
+      </c>
+      <c r="H51">
+        <v>0.2493714839220047</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>251</v>
+      </c>
+      <c r="C52" t="s">
+        <v>252</v>
+      </c>
+      <c r="D52" t="s">
+        <v>639</v>
+      </c>
+      <c r="E52">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="F52" t="s">
+        <v>254</v>
+      </c>
+      <c r="G52" t="s">
+        <v>254</v>
+      </c>
+      <c r="H52">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>256</v>
+      </c>
+      <c r="C53" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" t="s">
+        <v>640</v>
+      </c>
+      <c r="E53">
+        <v>0.5</v>
+      </c>
+      <c r="F53" t="s">
+        <v>259</v>
+      </c>
+      <c r="G53" t="s">
+        <v>259</v>
+      </c>
+      <c r="H53">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C54" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" t="s">
+        <v>262</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>264</v>
+      </c>
+      <c r="G54" t="s">
+        <v>264</v>
+      </c>
+      <c r="H54">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" t="s">
+        <v>266</v>
+      </c>
+      <c r="D55" t="s">
+        <v>535</v>
+      </c>
+      <c r="E55">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F55" t="s">
+        <v>268</v>
+      </c>
+      <c r="G55" t="s">
+        <v>268</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" t="s">
+        <v>271</v>
+      </c>
+      <c r="D56" t="s">
+        <v>641</v>
+      </c>
+      <c r="E56">
+        <v>0.75</v>
+      </c>
+      <c r="F56" t="s">
+        <v>273</v>
+      </c>
+      <c r="G56" t="s">
+        <v>642</v>
+      </c>
+      <c r="H56">
+        <v>0.37940970063209528</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" t="s">
+        <v>276</v>
+      </c>
+      <c r="D57" t="s">
+        <v>643</v>
+      </c>
+      <c r="E57">
+        <v>0.4</v>
+      </c>
+      <c r="F57" t="s">
+        <v>278</v>
+      </c>
+      <c r="G57" t="s">
+        <v>278</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>280</v>
+      </c>
+      <c r="C58" t="s">
+        <v>281</v>
+      </c>
+      <c r="D58" t="s">
+        <v>644</v>
+      </c>
+      <c r="E58">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F58" t="s">
+        <v>283</v>
+      </c>
+      <c r="G58" t="s">
+        <v>645</v>
+      </c>
+      <c r="H58">
+        <v>0.90978968143463135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>285</v>
+      </c>
+      <c r="C59" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" t="s">
+        <v>646</v>
+      </c>
+      <c r="E59">
+        <v>0.46153846153846162</v>
+      </c>
+      <c r="F59" t="s">
+        <v>288</v>
+      </c>
+      <c r="G59" t="s">
+        <v>647</v>
+      </c>
+      <c r="H59">
+        <v>0.59300005435943604</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>290</v>
+      </c>
+      <c r="C60" t="s">
+        <v>291</v>
+      </c>
+      <c r="D60" t="s">
+        <v>648</v>
+      </c>
+      <c r="E60">
+        <v>0.25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>293</v>
+      </c>
+      <c r="G60" t="s">
+        <v>293</v>
+      </c>
+      <c r="H60">
+        <v>0.99999994039535522</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" t="s">
+        <v>296</v>
+      </c>
+      <c r="D61" t="s">
+        <v>296</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>298</v>
+      </c>
+      <c r="G61" t="s">
+        <v>298</v>
+      </c>
+      <c r="H61">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>300</v>
+      </c>
+      <c r="C62" t="s">
+        <v>301</v>
+      </c>
+      <c r="D62" t="s">
+        <v>649</v>
+      </c>
+      <c r="E62">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="F62" t="s">
+        <v>303</v>
+      </c>
+      <c r="G62" t="s">
+        <v>303</v>
+      </c>
+      <c r="H62">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>305</v>
+      </c>
+      <c r="C63" t="s">
+        <v>306</v>
+      </c>
+      <c r="D63" t="s">
+        <v>650</v>
+      </c>
+      <c r="E63">
+        <v>0.2</v>
+      </c>
+      <c r="F63" t="s">
+        <v>308</v>
+      </c>
+      <c r="G63" t="s">
+        <v>651</v>
+      </c>
+      <c r="H63">
+        <v>0.5390007495880127</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>310</v>
+      </c>
+      <c r="C64" t="s">
+        <v>227</v>
+      </c>
+      <c r="D64" t="s">
+        <v>652</v>
+      </c>
+      <c r="E64">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="F64" t="s">
+        <v>229</v>
+      </c>
+      <c r="G64" t="s">
+        <v>229</v>
+      </c>
+      <c r="H64">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>312</v>
+      </c>
+      <c r="C65" t="s">
+        <v>313</v>
+      </c>
+      <c r="D65" t="s">
+        <v>313</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65" t="s">
+        <v>315</v>
+      </c>
+      <c r="G65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H65">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>317</v>
+      </c>
+      <c r="C66" t="s">
+        <v>318</v>
+      </c>
+      <c r="D66" t="s">
+        <v>653</v>
+      </c>
+      <c r="E66">
+        <v>0.2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>320</v>
+      </c>
+      <c r="G66" t="s">
+        <v>654</v>
+      </c>
+      <c r="H66">
+        <v>0.47954967617988592</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>322</v>
+      </c>
+      <c r="C67" t="s">
+        <v>323</v>
+      </c>
+      <c r="D67" t="s">
+        <v>655</v>
+      </c>
+      <c r="E67">
+        <v>0.4</v>
+      </c>
+      <c r="F67" t="s">
+        <v>325</v>
+      </c>
+      <c r="G67" t="s">
+        <v>656</v>
+      </c>
+      <c r="H67">
+        <v>0.85937333106994629</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>327</v>
+      </c>
+      <c r="C68" t="s">
+        <v>328</v>
+      </c>
+      <c r="D68" t="s">
+        <v>657</v>
+      </c>
+      <c r="E68">
+        <v>0.6</v>
+      </c>
+      <c r="F68" t="s">
+        <v>330</v>
+      </c>
+      <c r="G68" t="s">
+        <v>658</v>
+      </c>
+      <c r="H68">
+        <v>0.64197784662246704</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>332</v>
+      </c>
+      <c r="C69" t="s">
+        <v>333</v>
+      </c>
+      <c r="D69" t="s">
+        <v>659</v>
+      </c>
+      <c r="E69">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F69" t="s">
+        <v>335</v>
+      </c>
+      <c r="G69" t="s">
+        <v>335</v>
+      </c>
+      <c r="H69">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>337</v>
+      </c>
+      <c r="C70" t="s">
+        <v>338</v>
+      </c>
+      <c r="D70" t="s">
+        <v>338</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>340</v>
+      </c>
+      <c r="G70" t="s">
+        <v>340</v>
+      </c>
+      <c r="H70">
+        <v>0.99999994039535522</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>342</v>
+      </c>
+      <c r="C71" t="s">
+        <v>343</v>
+      </c>
+      <c r="D71" t="s">
+        <v>344</v>
+      </c>
+      <c r="E71">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="F71" t="s">
+        <v>345</v>
+      </c>
+      <c r="G71" t="s">
+        <v>346</v>
+      </c>
+      <c r="H71">
+        <v>0.79851973056793213</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>347</v>
+      </c>
+      <c r="C72" t="s">
+        <v>348</v>
+      </c>
+      <c r="D72" t="s">
+        <v>660</v>
+      </c>
+      <c r="E72">
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="F72" t="s">
+        <v>350</v>
+      </c>
+      <c r="G72" t="s">
+        <v>350</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>352</v>
+      </c>
+      <c r="C73" t="s">
+        <v>353</v>
+      </c>
+      <c r="D73" t="s">
+        <v>353</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>355</v>
+      </c>
+      <c r="G73" t="s">
+        <v>355</v>
+      </c>
+      <c r="H73">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>357</v>
+      </c>
+      <c r="C74" t="s">
+        <v>358</v>
+      </c>
+      <c r="D74" t="s">
+        <v>358</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>359</v>
+      </c>
+      <c r="G74" t="s">
+        <v>359</v>
+      </c>
+      <c r="H74">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>360</v>
+      </c>
+      <c r="C75" t="s">
+        <v>361</v>
+      </c>
+      <c r="D75" t="s">
+        <v>661</v>
+      </c>
+      <c r="E75">
+        <v>0.25</v>
+      </c>
+      <c r="F75" t="s">
+        <v>363</v>
+      </c>
+      <c r="G75" t="s">
+        <v>363</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>365</v>
+      </c>
+      <c r="C76" t="s">
+        <v>366</v>
+      </c>
+      <c r="D76" t="s">
+        <v>366</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>368</v>
+      </c>
+      <c r="G76" t="s">
+        <v>368</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>370</v>
+      </c>
+      <c r="C77" t="s">
+        <v>371</v>
+      </c>
+      <c r="D77" t="s">
+        <v>662</v>
+      </c>
+      <c r="E77">
+        <v>0.25</v>
+      </c>
+      <c r="F77" t="s">
+        <v>373</v>
+      </c>
+      <c r="G77" t="s">
+        <v>373</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>375</v>
+      </c>
+      <c r="C78" t="s">
+        <v>376</v>
+      </c>
+      <c r="D78" t="s">
+        <v>663</v>
+      </c>
+      <c r="E78">
+        <v>0.75</v>
+      </c>
+      <c r="F78" t="s">
+        <v>378</v>
+      </c>
+      <c r="G78" t="s">
+        <v>664</v>
+      </c>
+      <c r="H78">
+        <v>0.83503836393356323</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>380</v>
+      </c>
+      <c r="C79" t="s">
+        <v>381</v>
+      </c>
+      <c r="D79" t="s">
+        <v>665</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>383</v>
+      </c>
+      <c r="G79" t="s">
+        <v>666</v>
+      </c>
+      <c r="H79">
+        <v>0.24166867136955261</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>385</v>
+      </c>
+      <c r="C80" t="s">
+        <v>386</v>
+      </c>
+      <c r="D80" t="s">
+        <v>667</v>
+      </c>
+      <c r="E80">
+        <v>0.5</v>
+      </c>
+      <c r="F80" t="s">
+        <v>388</v>
+      </c>
+      <c r="G80" t="s">
+        <v>668</v>
+      </c>
+      <c r="H80">
+        <v>0.26109665632247919</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>390</v>
+      </c>
+      <c r="C81" t="s">
+        <v>391</v>
+      </c>
+      <c r="D81" t="s">
+        <v>669</v>
+      </c>
+      <c r="E81">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F81" t="s">
+        <v>393</v>
+      </c>
+      <c r="G81" t="s">
+        <v>670</v>
+      </c>
+      <c r="H81">
+        <v>0.53660047054290771</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>395</v>
+      </c>
+      <c r="C82" t="s">
+        <v>396</v>
+      </c>
+      <c r="D82" t="s">
+        <v>671</v>
+      </c>
+      <c r="E82">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F82" t="s">
+        <v>398</v>
+      </c>
+      <c r="G82" t="s">
+        <v>398</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>399</v>
+      </c>
+      <c r="C83" t="s">
+        <v>400</v>
+      </c>
+      <c r="D83" t="s">
+        <v>672</v>
+      </c>
+      <c r="E83">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="F83" t="s">
+        <v>402</v>
+      </c>
+      <c r="G83" t="s">
+        <v>402</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>404</v>
+      </c>
+      <c r="C84" t="s">
+        <v>405</v>
+      </c>
+      <c r="D84" t="s">
+        <v>673</v>
+      </c>
+      <c r="E84">
+        <v>1.25</v>
+      </c>
+      <c r="F84" t="s">
+        <v>406</v>
+      </c>
+      <c r="G84" t="s">
+        <v>674</v>
+      </c>
+      <c r="H84">
+        <v>0.98480850458145142</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" t="s">
+        <v>408</v>
+      </c>
+      <c r="D85" t="s">
+        <v>408</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85" t="s">
+        <v>410</v>
+      </c>
+      <c r="G85" t="s">
+        <v>410</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>84</v>
+      </c>
+      <c r="B86" t="s">
+        <v>412</v>
+      </c>
+      <c r="C86" t="s">
+        <v>413</v>
+      </c>
+      <c r="D86" t="s">
+        <v>413</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86" t="s">
+        <v>415</v>
+      </c>
+      <c r="G86" t="s">
+        <v>415</v>
+      </c>
+      <c r="H86">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>85</v>
+      </c>
+      <c r="B87" t="s">
+        <v>417</v>
+      </c>
+      <c r="C87" t="s">
+        <v>418</v>
+      </c>
+      <c r="D87" t="s">
+        <v>418</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="s">
+        <v>420</v>
+      </c>
+      <c r="G87" t="s">
+        <v>420</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="B88" t="s">
+        <v>422</v>
+      </c>
+      <c r="C88" t="s">
+        <v>423</v>
+      </c>
+      <c r="D88" t="s">
+        <v>675</v>
+      </c>
+      <c r="E88">
+        <v>0.25</v>
+      </c>
+      <c r="F88" t="s">
+        <v>425</v>
+      </c>
+      <c r="G88" t="s">
+        <v>425</v>
+      </c>
+      <c r="H88">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>87</v>
+      </c>
+      <c r="B89" t="s">
+        <v>426</v>
+      </c>
+      <c r="C89" t="s">
+        <v>427</v>
+      </c>
+      <c r="D89" t="s">
+        <v>427</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="s">
+        <v>429</v>
+      </c>
+      <c r="G89" t="s">
+        <v>429</v>
+      </c>
+      <c r="H89">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>88</v>
+      </c>
+      <c r="B90" t="s">
+        <v>431</v>
+      </c>
+      <c r="C90" t="s">
+        <v>432</v>
+      </c>
+      <c r="D90" t="s">
+        <v>432</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>434</v>
+      </c>
+      <c r="G90" t="s">
+        <v>434</v>
+      </c>
+      <c r="H90">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>436</v>
+      </c>
+      <c r="C91" t="s">
+        <v>437</v>
+      </c>
+      <c r="D91" t="s">
+        <v>437</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>439</v>
+      </c>
+      <c r="G91" t="s">
+        <v>439</v>
+      </c>
+      <c r="H91">
+        <v>0.9999997615814209</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>90</v>
+      </c>
+      <c r="B92" t="s">
+        <v>441</v>
+      </c>
+      <c r="C92" t="s">
+        <v>442</v>
+      </c>
+      <c r="D92" t="s">
+        <v>676</v>
+      </c>
+      <c r="E92">
+        <v>0.6</v>
+      </c>
+      <c r="F92" t="s">
+        <v>444</v>
+      </c>
+      <c r="G92" t="s">
+        <v>677</v>
+      </c>
+      <c r="H92">
+        <v>0.67245244979858398</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>91</v>
+      </c>
+      <c r="B93" t="s">
+        <v>446</v>
+      </c>
+      <c r="C93" t="s">
+        <v>447</v>
+      </c>
+      <c r="D93" t="s">
+        <v>447</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="s">
+        <v>449</v>
+      </c>
+      <c r="G93" t="s">
+        <v>449</v>
+      </c>
+      <c r="H93">
+        <v>0.99999988079071045</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>92</v>
+      </c>
+      <c r="B94" t="s">
+        <v>451</v>
+      </c>
+      <c r="C94" t="s">
+        <v>452</v>
+      </c>
+      <c r="D94" t="s">
+        <v>678</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>454</v>
+      </c>
+      <c r="G94" t="s">
+        <v>679</v>
+      </c>
+      <c r="H94">
+        <v>0.86750668287277222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>93</v>
+      </c>
+      <c r="B95" t="s">
+        <v>456</v>
+      </c>
+      <c r="C95" t="s">
+        <v>457</v>
+      </c>
+      <c r="D95" t="s">
+        <v>680</v>
+      </c>
+      <c r="E95">
+        <v>0.25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>459</v>
+      </c>
+      <c r="G95" t="s">
+        <v>459</v>
+      </c>
+      <c r="H95">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>94</v>
+      </c>
+      <c r="B96" t="s">
+        <v>461</v>
+      </c>
+      <c r="C96" t="s">
+        <v>681</v>
+      </c>
+      <c r="D96" t="s">
+        <v>682</v>
+      </c>
+      <c r="E96">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F96" t="s">
+        <v>464</v>
+      </c>
+      <c r="G96" t="s">
+        <v>683</v>
+      </c>
+      <c r="H96">
+        <v>0.46461623907089228</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>95</v>
+      </c>
+      <c r="B97" t="s">
+        <v>466</v>
+      </c>
+      <c r="C97" t="s">
+        <v>467</v>
+      </c>
+      <c r="D97" t="s">
+        <v>467</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" t="s">
+        <v>469</v>
+      </c>
+      <c r="G97" t="s">
+        <v>469</v>
+      </c>
+      <c r="H97">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>96</v>
+      </c>
+      <c r="B98" t="s">
+        <v>471</v>
+      </c>
+      <c r="C98" t="s">
+        <v>472</v>
+      </c>
+      <c r="D98" t="s">
+        <v>472</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98" t="s">
+        <v>474</v>
+      </c>
+      <c r="G98" t="s">
+        <v>474</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>97</v>
+      </c>
+      <c r="B99" t="s">
+        <v>476</v>
+      </c>
+      <c r="C99" t="s">
+        <v>477</v>
+      </c>
+      <c r="D99" t="s">
+        <v>477</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99" t="s">
+        <v>478</v>
+      </c>
+      <c r="G99" t="s">
+        <v>478</v>
+      </c>
+      <c r="H99">
+        <v>1.00000011920929</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>98</v>
+      </c>
+      <c r="B100" t="s">
+        <v>479</v>
+      </c>
+      <c r="C100" t="s">
+        <v>480</v>
+      </c>
+      <c r="D100" t="s">
+        <v>684</v>
+      </c>
+      <c r="E100">
+        <v>0.25</v>
+      </c>
+      <c r="F100" t="s">
+        <v>482</v>
+      </c>
+      <c r="G100" t="s">
+        <v>482</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>99</v>
+      </c>
+      <c r="B101" t="s">
+        <v>484</v>
+      </c>
+      <c r="C101" t="s">
+        <v>485</v>
+      </c>
+      <c r="D101" t="s">
+        <v>485</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>487</v>
+      </c>
+      <c r="G101" t="s">
+        <v>487</v>
+      </c>
+      <c r="H101">
+        <v>1.0000002384185791</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{209035B6-F535-41B6-A81A-8B7E05BECF26}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20.88671875" style="5" customWidth="1"/>
     <col min="3" max="3" width="20.88671875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" customWidth="1"/>
-    <col min="8" max="8" width="25.44140625" customWidth="1"/>
-    <col min="10" max="10" width="27.88671875" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" customWidth="1"/>
-    <col min="12" max="12" width="18.88671875" customWidth="1"/>
-    <col min="13" max="13" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" customWidth="1"/>
+    <col min="11" max="11" width="32" style="15" customWidth="1"/>
+    <col min="13" max="13" width="27.88671875" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.88671875" customWidth="1"/>
+    <col min="16" max="16" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>572</v>
       </c>
@@ -7547,23 +10519,32 @@
       <c r="C1" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="14" t="s">
+        <v>687</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K1" s="17" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>'whisper-base'!E2</f>
         <v>1</v>
@@ -7576,28 +10557,40 @@
         <f>B2-A2</f>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="16">
+        <f>wav2vec2_arabic!E2</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E2" s="6">
         <f>'whisper-base'!H2</f>
         <v>0.1002430841326714</v>
       </c>
-      <c r="E2" s="6">
+      <c r="F2" s="6">
         <f>'whisper-large-v3'!H2</f>
         <v>0.31530749797821039</v>
       </c>
-      <c r="F2">
-        <f>E2-D2</f>
+      <c r="G2">
+        <f>F2-E2</f>
         <v>0.21506441384553898</v>
       </c>
-      <c r="G2">
-        <f>IF(D2&gt;=0.75, 1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="H2" s="15">
+        <f>wav2vec2_arabic!H3</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I2">
         <f>IF(E2&gt;=0.75, 1, 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <f>IF(F2&gt;=0.75, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="15">
+        <f>IF(H2&gt;=0.75, 1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>'whisper-base'!E3</f>
         <v>1</v>
@@ -7610,28 +10603,40 @@
         <f t="shared" ref="C3:C66" si="0">B3-A3</f>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="16">
+        <f>wav2vec2_arabic!E3</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E3" s="6">
         <f>'whisper-base'!H3</f>
         <v>0.58972597122192383</v>
       </c>
-      <c r="E3" s="6">
+      <c r="F3" s="6">
         <f>'whisper-large-v3'!H3</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F66" si="1">E3-D3</f>
+      <c r="G3">
+        <f t="shared" ref="G3:G66" si="1">F3-E3</f>
         <v>0.41027426719665527</v>
       </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G66" si="2">IF(D3&gt;=0.75, 1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H66" si="3">IF(E3&gt;=0.75, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H3" s="15">
+        <f>wav2vec2_arabic!H4</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="2">IF(E3&gt;=0.75, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="3">IF(F3&gt;=0.75, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" ref="K3:K66" si="4">IF(H3&gt;=0.75, 1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>'whisper-base'!E4</f>
         <v>74</v>
@@ -7644,28 +10649,40 @@
         <f t="shared" si="0"/>
         <v>-74</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="16">
+        <f>wav2vec2_arabic!E4</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E4" s="6">
         <f>'whisper-base'!H4</f>
         <v>0.21664923429489141</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <f>'whisper-large-v3'!H4</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <f t="shared" si="1"/>
         <v>0.78335100412368774</v>
       </c>
-      <c r="G4">
+      <c r="H4" s="15">
+        <f>wav2vec2_arabic!H5</f>
+        <v>4.1545651853084557E-2</v>
+      </c>
+      <c r="I4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K4" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>'whisper-base'!E5</f>
         <v>0.83333333333333337</v>
@@ -7678,28 +10695,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="16">
+        <f>wav2vec2_arabic!E5</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
         <f>'whisper-base'!H5</f>
         <v>0.1188329309225082</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <f>'whisper-large-v3'!H5</f>
         <v>2.5657029822468761E-2</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <f t="shared" si="1"/>
         <v>-9.317590110003944E-2</v>
       </c>
-      <c r="G5">
+      <c r="H5" s="15">
+        <f>wav2vec2_arabic!H6</f>
+        <v>1</v>
+      </c>
+      <c r="I5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K5" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>'whisper-base'!E6</f>
         <v>0.625</v>
@@ -7712,31 +10741,43 @@
         <f t="shared" si="0"/>
         <v>-0.625</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="16">
+        <f>wav2vec2_arabic!E6</f>
+        <v>0.125</v>
+      </c>
+      <c r="E6" s="6">
         <f>'whisper-base'!H6</f>
         <v>0.72776049375534058</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <f>'whisper-large-v3'!H6</f>
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <f t="shared" si="1"/>
         <v>0.27223950624465942</v>
       </c>
-      <c r="G6">
+      <c r="H6" s="15">
+        <f>wav2vec2_arabic!H7</f>
+        <v>1</v>
+      </c>
+      <c r="I6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>'whisper-base'!E7</f>
         <v>0.2857142857142857</v>
@@ -7749,28 +10790,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="16">
+        <f>wav2vec2_arabic!E7</f>
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="E7" s="6">
         <f>'whisper-base'!H7</f>
         <v>1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <f>'whisper-large-v3'!H7</f>
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="H7" s="15">
+        <f>wav2vec2_arabic!H8</f>
+        <v>0.75318223237991333</v>
+      </c>
+      <c r="I7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K7" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>'whisper-base'!E8</f>
         <v>0.5</v>
@@ -7783,37 +10836,49 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="16">
+        <f>wav2vec2_arabic!E8</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
         <f>'whisper-base'!H8</f>
         <v>0.99999994039535522</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <f>'whisper-large-v3'!H8</f>
         <v>9.5533039420843124E-3</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <f t="shared" si="1"/>
         <v>-0.99044663645327091</v>
       </c>
-      <c r="G8">
+      <c r="H8" s="15">
+        <f>wav2vec2_arabic!H9</f>
+        <v>0.99999994039535522</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="M8" s="9" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="P8" s="9" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>'whisper-base'!E9</f>
         <v>0.8</v>
@@ -7826,42 +10891,55 @@
         <f t="shared" si="0"/>
         <v>-0.8</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="16">
+        <f>wav2vec2_arabic!E9</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
         <f>'whisper-base'!H9</f>
         <v>0.18284463882446289</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <f>'whisper-large-v3'!H9</f>
         <v>0.99999994039535522</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <f t="shared" si="1"/>
         <v>0.81715530157089233</v>
       </c>
-      <c r="G9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="H9" s="15">
+        <f>wav2vec2_arabic!H10</f>
+        <v>0.97012150287628174</v>
+      </c>
+      <c r="I9">
+        <f>IF(E9&gt;=0.75, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="K9" s="12">
+      <c r="N9" s="11">
         <f>AVERAGE(A2:A101)</f>
         <v>2.4656178266178266</v>
       </c>
-      <c r="L9" s="13">
+      <c r="O9" s="12">
         <f>AVERAGE(B2:B101)</f>
         <v>0.2730241147741147</v>
       </c>
-      <c r="M9" s="8" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P9" s="8">
+        <f>AVERAGE(D2:D101)</f>
+        <v>0.31215109890109888</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>'whisper-base'!E10</f>
         <v>1</v>
@@ -7874,42 +10952,55 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="16">
+        <f>wav2vec2_arabic!E10</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E10" s="6">
         <f>'whisper-base'!H10</f>
         <v>0.19802939891815191</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <f>'whisper-large-v3'!H10</f>
         <v>0.2176908552646637</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <f t="shared" si="1"/>
         <v>1.9661456346511785E-2</v>
       </c>
-      <c r="G10">
+      <c r="H10" s="15">
+        <f>wav2vec2_arabic!H11</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="K10" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="K10" s="12">
-        <f>AVERAGE(D2:D101)</f>
+      <c r="N10" s="11">
+        <f>AVERAGE(E2:E101)</f>
         <v>0.4486280328221619</v>
       </c>
-      <c r="L10" s="13">
-        <f>AVERAGE(E2:E101)</f>
+      <c r="O10" s="12">
+        <f>AVERAGE(F2:F101)</f>
         <v>0.82748323086649178</v>
       </c>
-      <c r="M10" s="8" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="P10" s="8">
+        <f>AVERAGE(H2:H101)</f>
+        <v>0.82001699712127452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>'whisper-base'!E11</f>
         <v>0.6</v>
@@ -7922,42 +11013,55 @@
         <f t="shared" si="0"/>
         <v>-0.6</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="16">
+        <f>wav2vec2_arabic!E11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
         <f>'whisper-base'!H11</f>
         <v>0.74012136459350586</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="6">
         <f>'whisper-large-v3'!H11</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <f t="shared" si="1"/>
         <v>0.25987875461578414</v>
       </c>
-      <c r="G11">
+      <c r="H11" s="15">
+        <f>wav2vec2_arabic!H12</f>
+        <v>1</v>
+      </c>
+      <c r="I11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="K11" s="12">
-        <f>AVERAGE(G2:G101)</f>
+      <c r="N11" s="11">
+        <f>AVERAGE(I2:I101)</f>
         <v>0.22</v>
       </c>
-      <c r="L11" s="13">
-        <f>AVERAGE(H2:H101)</f>
+      <c r="O11" s="12">
+        <f>AVERAGE(J2:J101)</f>
         <v>0.74</v>
       </c>
-      <c r="M11" s="8" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P11" s="9">
+        <f>AVERAGE(K2:K101)</f>
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>'whisper-base'!E12</f>
         <v>1.25</v>
@@ -7970,28 +11074,40 @@
         <f t="shared" si="0"/>
         <v>-0.75</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="16">
+        <f>wav2vec2_arabic!E12</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
         <f>'whisper-base'!H12</f>
         <v>0.59055274724960327</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="6">
         <f>'whisper-large-v3'!H12</f>
         <v>0.9158700704574585</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <f t="shared" si="1"/>
         <v>0.32531732320785522</v>
       </c>
-      <c r="G12">
+      <c r="H12" s="15">
+        <f>wav2vec2_arabic!H13</f>
+        <v>1</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K12" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>'whisper-base'!E13</f>
         <v>1.5</v>
@@ -8004,28 +11120,40 @@
         <f t="shared" si="0"/>
         <v>-1.5</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="16">
+        <f>wav2vec2_arabic!E13</f>
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="6">
         <f>'whisper-base'!H13</f>
         <v>0.26416093111038208</v>
       </c>
-      <c r="E13" s="6">
+      <c r="F13" s="6">
         <f>'whisper-large-v3'!H13</f>
         <v>1</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <f t="shared" si="1"/>
         <v>0.73583906888961792</v>
       </c>
-      <c r="G13">
+      <c r="H13" s="15">
+        <f>wav2vec2_arabic!H14</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K13" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>'whisper-base'!E14</f>
         <v>0.5</v>
@@ -8038,28 +11166,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="16">
+        <f>wav2vec2_arabic!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
         <f>'whisper-base'!H14</f>
         <v>0.46012073755264282</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="6">
         <f>'whisper-large-v3'!H14</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <f t="shared" si="1"/>
         <v>0.53987938165664717</v>
       </c>
-      <c r="G14">
+      <c r="H14" s="15">
+        <f>wav2vec2_arabic!H15</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K14" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>'whisper-base'!E15</f>
         <v>0.33333333333333331</v>
@@ -8072,28 +11212,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="16">
+        <f>wav2vec2_arabic!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
         <f>'whisper-base'!H15</f>
         <v>0.4161582887172699</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="6">
         <f>'whisper-large-v3'!H15</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <f t="shared" si="1"/>
         <v>0.5838418304920201</v>
       </c>
-      <c r="G15">
+      <c r="H15" s="15">
+        <f>wav2vec2_arabic!H16</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K15" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>'whisper-base'!E16</f>
         <v>1</v>
@@ -8106,28 +11258,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="16">
+        <f>wav2vec2_arabic!E16</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
         <f>'whisper-base'!H16</f>
         <v>0.46657714247703552</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="6">
         <f>'whisper-large-v3'!H16</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <f t="shared" si="1"/>
         <v>0.53342273831367493</v>
       </c>
-      <c r="G16">
+      <c r="H16" s="15">
+        <f>wav2vec2_arabic!H17</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K16" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>'whisper-base'!E17</f>
         <v>0.4</v>
@@ -8140,28 +11304,40 @@
         <f t="shared" si="0"/>
         <v>-0.4</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="16">
+        <f>wav2vec2_arabic!E17</f>
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="6">
         <f>'whisper-base'!H17</f>
         <v>0.84347999095916748</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="6">
         <f>'whisper-large-v3'!H17</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <f t="shared" si="1"/>
         <v>0.15651988983154297</v>
       </c>
-      <c r="G17">
+      <c r="H17" s="15">
+        <f>wav2vec2_arabic!H18</f>
+        <v>0.32088717818260187</v>
+      </c>
+      <c r="I17">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K17" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>'whisper-base'!E18</f>
         <v>0</v>
@@ -8174,28 +11350,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="16">
+        <f>wav2vec2_arabic!E18</f>
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="6">
         <f>'whisper-base'!H18</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="E18" s="6">
+      <c r="F18" s="6">
         <f>'whisper-large-v3'!H18</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18">
+      <c r="H18" s="15">
+        <f>wav2vec2_arabic!H19</f>
+        <v>0.99999994039535522</v>
+      </c>
+      <c r="I18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K18" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>'whisper-base'!E19</f>
         <v>1</v>
@@ -8208,28 +11396,40 @@
         <f t="shared" si="0"/>
         <v>-0.6</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="16">
+        <f>wav2vec2_arabic!E19</f>
+        <v>0.2</v>
+      </c>
+      <c r="E19" s="6">
         <f>'whisper-base'!H19</f>
         <v>0.23220984637737269</v>
       </c>
-      <c r="E19" s="6">
+      <c r="F19" s="6">
         <f>'whisper-large-v3'!H19</f>
         <v>0.99999994039535522</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <f t="shared" si="1"/>
         <v>0.76779009401798248</v>
       </c>
-      <c r="G19">
+      <c r="H19" s="15">
+        <f>wav2vec2_arabic!H20</f>
+        <v>0.54973769187927246</v>
+      </c>
+      <c r="I19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K19" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>'whisper-base'!E20</f>
         <v>0.75</v>
@@ -8242,28 +11442,40 @@
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="16">
+        <f>wav2vec2_arabic!E20</f>
+        <v>0.5</v>
+      </c>
+      <c r="E20" s="6">
         <f>'whisper-base'!H20</f>
         <v>0.52792418003082275</v>
       </c>
-      <c r="E20" s="6">
+      <c r="F20" s="6">
         <f>'whisper-large-v3'!H20</f>
         <v>0.77473193407058716</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <f t="shared" si="1"/>
         <v>0.2468077540397644</v>
       </c>
-      <c r="G20">
+      <c r="H20" s="15">
+        <f>wav2vec2_arabic!H21</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K20" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>'whisper-base'!E21</f>
         <v>1</v>
@@ -8276,28 +11488,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="16">
+        <f>wav2vec2_arabic!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="6">
         <f>'whisper-base'!H21</f>
         <v>0.15250527858734131</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F21" s="6">
         <f>'whisper-large-v3'!H21</f>
         <v>0.129649743437767</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <f t="shared" si="1"/>
         <v>-2.2855535149574308E-2</v>
       </c>
-      <c r="G21">
+      <c r="H21" s="15">
+        <f>wav2vec2_arabic!H22</f>
+        <v>0.90663361549377441</v>
+      </c>
+      <c r="I21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K21" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>'whisper-base'!E22</f>
         <v>1</v>
@@ -8310,28 +11534,40 @@
         <f t="shared" si="0"/>
         <v>-0.1428571428571429</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="16">
+        <f>wav2vec2_arabic!E22</f>
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="E22" s="6">
         <f>'whisper-base'!H22</f>
         <v>1.788007095456123E-2</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F22" s="6">
         <f>'whisper-large-v3'!H22</f>
         <v>0.37579643726348883</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <f t="shared" si="1"/>
         <v>0.35791636630892759</v>
       </c>
-      <c r="G22">
+      <c r="H22" s="15">
+        <f>wav2vec2_arabic!H23</f>
+        <v>0.84008181095123291</v>
+      </c>
+      <c r="I22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K22" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>'whisper-base'!E23</f>
         <v>1</v>
@@ -8344,28 +11580,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="16">
+        <f>wav2vec2_arabic!E23</f>
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="6">
         <f>'whisper-base'!H23</f>
         <v>0.37175759673118591</v>
       </c>
-      <c r="E23" s="6">
+      <c r="F23" s="6">
         <f>'whisper-large-v3'!H23</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <f t="shared" si="1"/>
         <v>0.62824252247810408</v>
       </c>
-      <c r="G23">
+      <c r="H23" s="15">
+        <f>wav2vec2_arabic!H24</f>
+        <v>0.9999997615814209</v>
+      </c>
+      <c r="I23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K23" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>'whisper-base'!E24</f>
         <v>0.75</v>
@@ -8378,28 +11626,40 @@
         <f t="shared" si="0"/>
         <v>-0.75</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="16">
+        <f>wav2vec2_arabic!E24</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
         <f>'whisper-base'!H24</f>
         <v>0.23692888021469119</v>
       </c>
-      <c r="E24" s="6">
+      <c r="F24" s="6">
         <f>'whisper-large-v3'!H24</f>
         <v>0.9999997615814209</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <f t="shared" si="1"/>
         <v>0.76307088136672974</v>
       </c>
-      <c r="G24">
+      <c r="H24" s="15">
+        <f>wav2vec2_arabic!H25</f>
+        <v>0.31205347180366522</v>
+      </c>
+      <c r="I24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K24" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>'whisper-base'!E25</f>
         <v>1.5</v>
@@ -8412,28 +11672,40 @@
         <f t="shared" si="0"/>
         <v>-0.75</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="16">
+        <f>wav2vec2_arabic!E25</f>
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="6">
         <f>'whisper-base'!H25</f>
         <v>0.13610383868217471</v>
       </c>
-      <c r="E25" s="6">
+      <c r="F25" s="6">
         <f>'whisper-large-v3'!H25</f>
         <v>0.74079340696334839</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <f t="shared" si="1"/>
         <v>0.60468956828117371</v>
       </c>
-      <c r="G25">
+      <c r="H25" s="15">
+        <f>wav2vec2_arabic!H26</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K25" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>'whisper-base'!E26</f>
         <v>1</v>
@@ -8446,28 +11718,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="16">
+        <f>wav2vec2_arabic!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
         <f>'whisper-base'!H26</f>
         <v>0.12500423192977911</v>
       </c>
-      <c r="E26" s="6">
+      <c r="F26" s="6">
         <f>'whisper-large-v3'!H26</f>
         <v>0.11797945946455</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <f t="shared" si="1"/>
         <v>-7.0247724652291038E-3</v>
       </c>
-      <c r="G26">
+      <c r="H26" s="15">
+        <f>wav2vec2_arabic!H27</f>
+        <v>0.22744505107402799</v>
+      </c>
+      <c r="I26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K26" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>'whisper-base'!E27</f>
         <v>0.8</v>
@@ -8480,28 +11764,40 @@
         <f t="shared" si="0"/>
         <v>-0.60000000000000009</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="16">
+        <f>wav2vec2_arabic!E27</f>
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="6">
         <f>'whisper-base'!H27</f>
         <v>3.3954005688428879E-2</v>
       </c>
-      <c r="E27" s="6">
+      <c r="F27" s="6">
         <f>'whisper-large-v3'!H27</f>
         <v>0.2430822551250458</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <f t="shared" si="1"/>
         <v>0.20912824943661693</v>
       </c>
-      <c r="G27">
+      <c r="H27" s="15">
+        <f>wav2vec2_arabic!H28</f>
+        <v>5.7809960097074509E-2</v>
+      </c>
+      <c r="I27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K27" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>'whisper-base'!E28</f>
         <v>1</v>
@@ -8514,28 +11810,40 @@
         <f t="shared" si="0"/>
         <v>-0.25</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="16">
+        <f>wav2vec2_arabic!E28</f>
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
         <f>'whisper-base'!H28</f>
         <v>-5.4810993373394012E-2</v>
       </c>
-      <c r="E28" s="6">
+      <c r="F28" s="6">
         <f>'whisper-large-v3'!H28</f>
         <v>-3.4812513738870621E-2</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <f t="shared" si="1"/>
         <v>1.9998479634523392E-2</v>
       </c>
-      <c r="G28">
+      <c r="H28" s="15">
+        <f>wav2vec2_arabic!H29</f>
+        <v>0.82445734739303589</v>
+      </c>
+      <c r="I28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K28" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>'whisper-base'!E29</f>
         <v>1</v>
@@ -8548,28 +11856,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="16">
+        <f>wav2vec2_arabic!E29</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E29" s="6">
         <f>'whisper-base'!H29</f>
         <v>0.1168616712093353</v>
       </c>
-      <c r="E29" s="6">
+      <c r="F29" s="6">
         <f>'whisper-large-v3'!H29</f>
         <v>0.67086195945739746</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <f t="shared" si="1"/>
         <v>0.55400028824806213</v>
       </c>
-      <c r="G29">
+      <c r="H29" s="15">
+        <f>wav2vec2_arabic!H30</f>
+        <v>8.5401400923728943E-2</v>
+      </c>
+      <c r="I29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K29" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>'whisper-base'!E30</f>
         <v>1</v>
@@ -8582,28 +11902,40 @@
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="16">
+        <f>wav2vec2_arabic!E30</f>
+        <v>1</v>
+      </c>
+      <c r="E30" s="6">
         <f>'whisper-base'!H30</f>
         <v>7.311566174030304E-2</v>
       </c>
-      <c r="E30" s="6">
+      <c r="F30" s="6">
         <f>'whisper-large-v3'!H30</f>
         <v>0.54233396053314209</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <f t="shared" si="1"/>
         <v>0.46921829879283905</v>
       </c>
-      <c r="G30">
+      <c r="H30" s="15">
+        <f>wav2vec2_arabic!H31</f>
+        <v>0.3049854040145874</v>
+      </c>
+      <c r="I30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K30" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>'whisper-base'!E31</f>
         <v>1</v>
@@ -8616,28 +11948,40 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="16">
+        <f>wav2vec2_arabic!E31</f>
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
         <f>'whisper-base'!H31</f>
         <v>0.18337370455265051</v>
       </c>
-      <c r="E31" s="6">
+      <c r="F31" s="6">
         <f>'whisper-large-v3'!H31</f>
         <v>0.13280749320983889</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <f t="shared" si="1"/>
         <v>-5.0566211342811612E-2</v>
       </c>
-      <c r="G31">
+      <c r="H31" s="15">
+        <f>wav2vec2_arabic!H32</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K31" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>'whisper-base'!E32</f>
         <v>0</v>
@@ -8650,28 +11994,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="16">
+        <f>wav2vec2_arabic!E32</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
         <f>'whisper-base'!H32</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="E32" s="6">
+      <c r="F32" s="6">
         <f>'whisper-large-v3'!H32</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G32">
+      <c r="H32" s="15">
+        <f>wav2vec2_arabic!H33</f>
+        <v>1</v>
+      </c>
+      <c r="I32">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H32">
+      <c r="J32">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K32" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>'whisper-base'!E33</f>
         <v>1</v>
@@ -8684,28 +12040,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="16">
+        <f>wav2vec2_arabic!E33</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="6">
         <f>'whisper-base'!H33</f>
         <v>0.42341235280036932</v>
       </c>
-      <c r="E33" s="6">
+      <c r="F33" s="6">
         <f>'whisper-large-v3'!H33</f>
         <v>1</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <f t="shared" si="1"/>
         <v>0.57658764719963074</v>
       </c>
-      <c r="G33">
+      <c r="H33" s="15">
+        <f>wav2vec2_arabic!H34</f>
+        <v>0.60369712114334106</v>
+      </c>
+      <c r="I33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K33" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>'whisper-base'!E34</f>
         <v>64</v>
@@ -8718,28 +12086,40 @@
         <f t="shared" si="0"/>
         <v>-63</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="16">
+        <f>wav2vec2_arabic!E34</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="6">
         <f>'whisper-base'!H34</f>
         <v>0.14046585559844971</v>
       </c>
-      <c r="E34" s="6">
+      <c r="F34" s="6">
         <f>'whisper-large-v3'!H34</f>
         <v>0.62342619895935059</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <f t="shared" si="1"/>
         <v>0.48296034336090088</v>
       </c>
-      <c r="G34">
+      <c r="H34" s="15">
+        <f>wav2vec2_arabic!H35</f>
+        <v>0.44888666272163391</v>
+      </c>
+      <c r="I34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K34" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <f>'whisper-base'!E35</f>
         <v>0.8571428571428571</v>
@@ -8752,28 +12132,40 @@
         <f t="shared" si="0"/>
         <v>-0.7142857142857143</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="16">
+        <f>wav2vec2_arabic!E35</f>
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="E35" s="6">
         <f>'whisper-base'!H35</f>
         <v>0.15373677015304571</v>
       </c>
-      <c r="E35" s="6">
+      <c r="F35" s="6">
         <f>'whisper-large-v3'!H35</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <f t="shared" si="1"/>
         <v>0.84626311063766479</v>
       </c>
-      <c r="G35">
+      <c r="H35" s="15">
+        <f>wav2vec2_arabic!H36</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I35">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K35" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <f>'whisper-base'!E36</f>
         <v>0.4</v>
@@ -8786,28 +12178,40 @@
         <f t="shared" si="0"/>
         <v>-0.4</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="16">
+        <f>wav2vec2_arabic!E36</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="6">
         <f>'whisper-base'!H36</f>
         <v>0.79385626316070557</v>
       </c>
-      <c r="E36" s="6">
+      <c r="F36" s="6">
         <f>'whisper-large-v3'!H36</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <f t="shared" si="1"/>
         <v>0.20614361763000488</v>
       </c>
-      <c r="G36">
+      <c r="H36" s="15">
+        <f>wav2vec2_arabic!H37</f>
+        <v>0.71904122829437256</v>
+      </c>
+      <c r="I36">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K36" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <f>'whisper-base'!E37</f>
         <v>0.33333333333333331</v>
@@ -8820,28 +12224,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="16">
+        <f>wav2vec2_arabic!E37</f>
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="E37" s="6">
         <f>'whisper-base'!H37</f>
         <v>0.68035244941711426</v>
       </c>
-      <c r="E37" s="6">
+      <c r="F37" s="6">
         <f>'whisper-large-v3'!H37</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <f t="shared" si="1"/>
         <v>0.31964743137359619</v>
       </c>
-      <c r="G37">
+      <c r="H37" s="15">
+        <f>wav2vec2_arabic!H38</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K37" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <f>'whisper-base'!E38</f>
         <v>1</v>
@@ -8854,28 +12270,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="16">
+        <f>wav2vec2_arabic!E38</f>
+        <v>1</v>
+      </c>
+      <c r="E38" s="6">
         <f>'whisper-base'!H38</f>
         <v>6.119241937994957E-2</v>
       </c>
-      <c r="E38" s="6">
+      <c r="F38" s="6">
         <f>'whisper-large-v3'!H38</f>
         <v>0.32589805126190191</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <f t="shared" si="1"/>
         <v>0.26470563188195234</v>
       </c>
-      <c r="G38">
+      <c r="H38" s="15">
+        <f>wav2vec2_arabic!H39</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K38" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <f>'whisper-base'!E39</f>
         <v>0.66666666666666663</v>
@@ -8888,28 +12316,40 @@
         <f t="shared" si="0"/>
         <v>-0.66666666666666663</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="16">
+        <f>wav2vec2_arabic!E39</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E39" s="6">
         <f>'whisper-base'!H39</f>
         <v>0.93123674392700195</v>
       </c>
-      <c r="E39" s="6">
+      <c r="F39" s="6">
         <f>'whisper-large-v3'!H39</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <f t="shared" si="1"/>
         <v>6.8763375282288042E-2</v>
       </c>
-      <c r="G39">
+      <c r="H39" s="15">
+        <f>wav2vec2_arabic!H40</f>
+        <v>1</v>
+      </c>
+      <c r="I39">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K39" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <f>'whisper-base'!E40</f>
         <v>0.25</v>
@@ -8922,28 +12362,40 @@
         <f t="shared" si="0"/>
         <v>-0.25</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="16">
+        <f>wav2vec2_arabic!E40</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="6">
         <f>'whisper-base'!H40</f>
         <v>0.53685164451599121</v>
       </c>
-      <c r="E40" s="6">
+      <c r="F40" s="6">
         <f>'whisper-large-v3'!H40</f>
         <v>1</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <f t="shared" si="1"/>
         <v>0.46314835548400879</v>
       </c>
-      <c r="G40">
+      <c r="H40" s="15">
+        <f>wav2vec2_arabic!H41</f>
+        <v>0.43706187605857849</v>
+      </c>
+      <c r="I40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K40" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <f>'whisper-base'!E41</f>
         <v>0.5</v>
@@ -8956,28 +12408,40 @@
         <f t="shared" si="0"/>
         <v>-0.25</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="16">
+        <f>wav2vec2_arabic!E41</f>
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="6">
         <f>'whisper-base'!H41</f>
         <v>0.89452874660491943</v>
       </c>
-      <c r="E41" s="6">
+      <c r="F41" s="6">
         <f>'whisper-large-v3'!H41</f>
         <v>0.9838874340057373</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <f t="shared" si="1"/>
         <v>8.9358687400817871E-2</v>
       </c>
-      <c r="G41">
+      <c r="H41" s="15">
+        <f>wav2vec2_arabic!H42</f>
+        <v>1</v>
+      </c>
+      <c r="I41">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K41" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <f>'whisper-base'!E42</f>
         <v>0.42857142857142849</v>
@@ -8990,28 +12454,40 @@
         <f t="shared" si="0"/>
         <v>-0.42857142857142849</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="16">
+        <f>wav2vec2_arabic!E42</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="6">
         <f>'whisper-base'!H42</f>
         <v>0.95409530401229858</v>
       </c>
-      <c r="E42" s="6">
+      <c r="F42" s="6">
         <f>'whisper-large-v3'!H42</f>
         <v>1</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <f t="shared" si="1"/>
         <v>4.5904695987701416E-2</v>
       </c>
-      <c r="G42">
+      <c r="H42" s="15">
+        <f>wav2vec2_arabic!H43</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I42">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K42" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <f>'whisper-base'!E43</f>
         <v>0.4</v>
@@ -9024,28 +12500,40 @@
         <f t="shared" si="0"/>
         <v>-0.4</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="16">
+        <f>wav2vec2_arabic!E43</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="6">
         <f>'whisper-base'!H43</f>
         <v>0.57102739810943604</v>
       </c>
-      <c r="E43" s="6">
+      <c r="F43" s="6">
         <f>'whisper-large-v3'!H43</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <f t="shared" si="1"/>
         <v>0.42897248268127441</v>
       </c>
-      <c r="G43">
+      <c r="H43" s="15">
+        <f>wav2vec2_arabic!H44</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K43" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <f>'whisper-base'!E44</f>
         <v>0.66666666666666663</v>
@@ -9058,28 +12546,40 @@
         <f t="shared" si="0"/>
         <v>-0.66666666666666663</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="16">
+        <f>wav2vec2_arabic!E44</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="6">
         <f>'whisper-base'!H44</f>
         <v>0.2242375314235687</v>
       </c>
-      <c r="E44" s="6">
+      <c r="F44" s="6">
         <f>'whisper-large-v3'!H44</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <f t="shared" si="1"/>
         <v>0.77576270699501038</v>
       </c>
-      <c r="G44">
+      <c r="H44" s="15">
+        <f>wav2vec2_arabic!H45</f>
+        <v>9.0471811592578888E-2</v>
+      </c>
+      <c r="I44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K44" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <f>'whisper-base'!E45</f>
         <v>1</v>
@@ -9092,28 +12592,40 @@
         <f t="shared" si="0"/>
         <v>-0.83333333333333326</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="16">
+        <f>wav2vec2_arabic!E45</f>
+        <v>0.5</v>
+      </c>
+      <c r="E45" s="6">
         <f>'whisper-base'!H45</f>
         <v>0.17273461818695071</v>
       </c>
-      <c r="E45" s="6">
+      <c r="F45" s="6">
         <f>'whisper-large-v3'!H45</f>
         <v>0.98609328269958496</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <f t="shared" si="1"/>
         <v>0.81335866451263428</v>
       </c>
-      <c r="G45">
+      <c r="H45" s="15">
+        <f>wav2vec2_arabic!H46</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H45">
+      <c r="J45">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K45" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <f>'whisper-base'!E46</f>
         <v>0.75</v>
@@ -9126,28 +12638,40 @@
         <f t="shared" si="0"/>
         <v>-0.25</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="16">
+        <f>wav2vec2_arabic!E46</f>
+        <v>0.25</v>
+      </c>
+      <c r="E46" s="6">
         <f>'whisper-base'!H46</f>
         <v>0.36288589239120478</v>
       </c>
-      <c r="E46" s="6">
+      <c r="F46" s="6">
         <f>'whisper-large-v3'!H46</f>
         <v>0.28415319323539728</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <f t="shared" si="1"/>
         <v>-7.8732699155807495E-2</v>
       </c>
-      <c r="G46">
+      <c r="H46" s="15">
+        <f>wav2vec2_arabic!H47</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K46" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <f>'whisper-base'!E47</f>
         <v>0.5</v>
@@ -9160,28 +12684,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333326</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="16">
+        <f>wav2vec2_arabic!E47</f>
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="E47" s="6">
         <f>'whisper-base'!H47</f>
         <v>0.66976898908615112</v>
       </c>
-      <c r="E47" s="6">
+      <c r="F47" s="6">
         <f>'whisper-large-v3'!H47</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <f t="shared" si="1"/>
         <v>0.33023089170455933</v>
       </c>
-      <c r="G47">
+      <c r="H47" s="15">
+        <f>wav2vec2_arabic!H48</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I47">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K47" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <f>'whisper-base'!E48</f>
         <v>1</v>
@@ -9194,28 +12730,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="16">
+        <f>wav2vec2_arabic!E48</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="6">
         <f>'whisper-base'!H48</f>
         <v>0.26307851076126099</v>
       </c>
-      <c r="E48" s="6">
+      <c r="F48" s="6">
         <f>'whisper-large-v3'!H48</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <f t="shared" si="1"/>
         <v>0.73692137002944946</v>
       </c>
-      <c r="G48">
+      <c r="H48" s="15">
+        <f>wav2vec2_arabic!H49</f>
+        <v>0.99999982118606567</v>
+      </c>
+      <c r="I48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K48" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <f>'whisper-base'!E49</f>
         <v>1</v>
@@ -9228,28 +12776,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="16">
+        <f>wav2vec2_arabic!E49</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
         <f>'whisper-base'!H49</f>
         <v>0.43307942152023321</v>
       </c>
-      <c r="E49" s="6">
+      <c r="F49" s="6">
         <f>'whisper-large-v3'!H49</f>
         <v>0.99999982118606567</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <f t="shared" si="1"/>
         <v>0.56692039966583252</v>
       </c>
-      <c r="G49">
+      <c r="H49" s="15">
+        <f>wav2vec2_arabic!H50</f>
+        <v>0.19441559910774231</v>
+      </c>
+      <c r="I49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H49">
+      <c r="J49">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K49" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <f>'whisper-base'!E50</f>
         <v>0.55555555555555558</v>
@@ -9262,28 +12822,40 @@
         <f t="shared" si="0"/>
         <v>-0.44444444444444448</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="16">
+        <f>wav2vec2_arabic!E50</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E50" s="6">
         <f>'whisper-base'!H50</f>
         <v>0.41294416785240168</v>
       </c>
-      <c r="E50" s="6">
+      <c r="F50" s="6">
         <f>'whisper-large-v3'!H50</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <f t="shared" si="1"/>
         <v>0.58705595135688826</v>
       </c>
-      <c r="G50">
+      <c r="H50" s="15">
+        <f>wav2vec2_arabic!H51</f>
+        <v>0.2493714839220047</v>
+      </c>
+      <c r="I50">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K50" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <f>'whisper-base'!E51</f>
         <v>1</v>
@@ -9296,28 +12868,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="16">
+        <f>wav2vec2_arabic!E51</f>
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="E51" s="6">
         <f>'whisper-base'!H51</f>
         <v>0.15415400266647339</v>
       </c>
-      <c r="E51" s="6">
+      <c r="F51" s="6">
         <f>'whisper-large-v3'!H51</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <f t="shared" si="1"/>
         <v>0.84584611654281661</v>
       </c>
-      <c r="G51">
+      <c r="H51" s="15">
+        <f>wav2vec2_arabic!H52</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I51">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H51">
+      <c r="J51">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K51" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <f>'whisper-base'!E52</f>
         <v>1</v>
@@ -9330,28 +12914,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="16">
+        <f>wav2vec2_arabic!E52</f>
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="E52" s="6">
         <f>'whisper-base'!H52</f>
         <v>3.3694440498948102E-3</v>
       </c>
-      <c r="E52" s="6">
+      <c r="F52" s="6">
         <f>'whisper-large-v3'!H52</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <f t="shared" si="1"/>
         <v>0.99663043674081564</v>
       </c>
-      <c r="G52">
+      <c r="H52" s="15">
+        <f>wav2vec2_arabic!H53</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H52">
+      <c r="J52">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K52" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <f>'whisper-base'!E53</f>
         <v>1</v>
@@ -9364,28 +12960,40 @@
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="16">
+        <f>wav2vec2_arabic!E53</f>
+        <v>0.5</v>
+      </c>
+      <c r="E53" s="6">
         <f>'whisper-base'!H53</f>
         <v>0.1452281326055527</v>
       </c>
-      <c r="E53" s="6">
+      <c r="F53" s="6">
         <f>'whisper-large-v3'!H53</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <f t="shared" si="1"/>
         <v>0.85477210581302643</v>
       </c>
-      <c r="G53">
+      <c r="H53" s="15">
+        <f>wav2vec2_arabic!H54</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H53">
+      <c r="J53">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K53" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <f>'whisper-base'!E54</f>
         <v>0.25</v>
@@ -9398,28 +13006,40 @@
         <f t="shared" si="0"/>
         <v>-0.25</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="16">
+        <f>wav2vec2_arabic!E54</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="6">
         <f>'whisper-base'!H54</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="E54" s="6">
+      <c r="F54" s="6">
         <f>'whisper-large-v3'!H54</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G54">
+      <c r="H54" s="15">
+        <f>wav2vec2_arabic!H55</f>
+        <v>1</v>
+      </c>
+      <c r="I54">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H54">
+      <c r="J54">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K54" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <f>'whisper-base'!E55</f>
         <v>0.7142857142857143</v>
@@ -9432,28 +13052,40 @@
         <f t="shared" si="0"/>
         <v>-0.4285714285714286</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="16">
+        <f>wav2vec2_arabic!E55</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="E55" s="6">
         <f>'whisper-base'!H55</f>
         <v>0.71379321813583374</v>
       </c>
-      <c r="E55" s="6">
+      <c r="F55" s="6">
         <f>'whisper-large-v3'!H55</f>
         <v>1</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <f t="shared" si="1"/>
         <v>0.28620678186416626</v>
       </c>
-      <c r="G55">
+      <c r="H55" s="15">
+        <f>wav2vec2_arabic!H56</f>
+        <v>0.37940970063209528</v>
+      </c>
+      <c r="I55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H55">
+      <c r="J55">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K55" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <f>'whisper-base'!E56</f>
         <v>1</v>
@@ -9466,28 +13098,40 @@
         <f t="shared" si="0"/>
         <v>-0.25</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="16">
+        <f>wav2vec2_arabic!E56</f>
+        <v>0.75</v>
+      </c>
+      <c r="E56" s="6">
         <f>'whisper-base'!H56</f>
         <v>0.40583360195159912</v>
       </c>
-      <c r="E56" s="6">
+      <c r="F56" s="6">
         <f>'whisper-large-v3'!H56</f>
         <v>1</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <f t="shared" si="1"/>
         <v>0.59416639804840088</v>
       </c>
-      <c r="G56">
+      <c r="H56" s="15">
+        <f>wav2vec2_arabic!H57</f>
+        <v>1</v>
+      </c>
+      <c r="I56">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H56">
+      <c r="J56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K56" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <f>'whisper-base'!E57</f>
         <v>0.2</v>
@@ -9500,28 +13144,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="16">
+        <f>wav2vec2_arabic!E57</f>
+        <v>0.4</v>
+      </c>
+      <c r="E57" s="6">
         <f>'whisper-base'!H57</f>
         <v>0.75294989347457886</v>
       </c>
-      <c r="E57" s="6">
+      <c r="F57" s="6">
         <f>'whisper-large-v3'!H57</f>
         <v>0.91474443674087524</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <f t="shared" si="1"/>
         <v>0.16179454326629639</v>
       </c>
-      <c r="G57">
+      <c r="H57" s="15">
+        <f>wav2vec2_arabic!H58</f>
+        <v>0.90978968143463135</v>
+      </c>
+      <c r="I57">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H57">
+      <c r="J57">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K57" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <f>'whisper-base'!E58</f>
         <v>1</v>
@@ -9534,28 +13190,40 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="16">
+        <f>wav2vec2_arabic!E58</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E58" s="6">
         <f>'whisper-base'!H58</f>
         <v>0.21768653392791751</v>
       </c>
-      <c r="E58" s="6">
+      <c r="F58" s="6">
         <f>'whisper-large-v3'!H58</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <f t="shared" si="1"/>
         <v>0.78231334686279297</v>
       </c>
-      <c r="G58">
+      <c r="H58" s="15">
+        <f>wav2vec2_arabic!H59</f>
+        <v>0.59300005435943604</v>
+      </c>
+      <c r="I58">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H58">
+      <c r="J58">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K58" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <f>'whisper-base'!E59</f>
         <v>1.153846153846154</v>
@@ -9568,28 +13236,40 @@
         <f t="shared" si="0"/>
         <v>-0.69230769230769229</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="16">
+        <f>wav2vec2_arabic!E59</f>
+        <v>0.46153846153846162</v>
+      </c>
+      <c r="E59" s="6">
         <f>'whisper-base'!H59</f>
         <v>0.1140464693307877</v>
       </c>
-      <c r="E59" s="6">
+      <c r="F59" s="6">
         <f>'whisper-large-v3'!H59</f>
         <v>0.51742255687713623</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <f t="shared" si="1"/>
         <v>0.40337608754634852</v>
       </c>
-      <c r="G59">
+      <c r="H59" s="15">
+        <f>wav2vec2_arabic!H60</f>
+        <v>0.99999994039535522</v>
+      </c>
+      <c r="I59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H59">
+      <c r="J59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K59" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <f>'whisper-base'!E60</f>
         <v>0.75</v>
@@ -9602,28 +13282,40 @@
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="16">
+        <f>wav2vec2_arabic!E60</f>
+        <v>0.25</v>
+      </c>
+      <c r="E60" s="6">
         <f>'whisper-base'!H60</f>
         <v>0.14907167851924899</v>
       </c>
-      <c r="E60" s="6">
+      <c r="F60" s="6">
         <f>'whisper-large-v3'!H60</f>
         <v>0.99999994039535522</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <f t="shared" si="1"/>
         <v>0.85092826187610626</v>
       </c>
-      <c r="G60">
+      <c r="H60" s="15">
+        <f>wav2vec2_arabic!H61</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H60">
+      <c r="J60">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K60" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <f>'whisper-base'!E61</f>
         <v>1</v>
@@ -9636,28 +13328,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="16">
+        <f>wav2vec2_arabic!E61</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="6">
         <f>'whisper-base'!H61</f>
         <v>0.30048099160194403</v>
       </c>
-      <c r="E61" s="6">
+      <c r="F61" s="6">
         <f>'whisper-large-v3'!H61</f>
         <v>0.6374351978302002</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <f t="shared" si="1"/>
         <v>0.33695420622825617</v>
       </c>
-      <c r="G61">
+      <c r="H61" s="15">
+        <f>wav2vec2_arabic!H62</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I61">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H61">
+      <c r="J61">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K61" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <f>'whisper-base'!E62</f>
         <v>0.7142857142857143</v>
@@ -9670,28 +13374,40 @@
         <f t="shared" si="0"/>
         <v>-0.28571428571428581</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="16">
+        <f>wav2vec2_arabic!E62</f>
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="E62" s="6">
         <f>'whisper-base'!H62</f>
         <v>0.44257825613021851</v>
       </c>
-      <c r="E62" s="6">
+      <c r="F62" s="6">
         <f>'whisper-large-v3'!H62</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <f t="shared" si="1"/>
         <v>0.5574219822883606</v>
       </c>
-      <c r="G62">
+      <c r="H62" s="15">
+        <f>wav2vec2_arabic!H63</f>
+        <v>0.5390007495880127</v>
+      </c>
+      <c r="I62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H62">
+      <c r="J62">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K62" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <f>'whisper-base'!E63</f>
         <v>0.6</v>
@@ -9704,28 +13420,40 @@
         <f t="shared" si="0"/>
         <v>-0.6</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="16">
+        <f>wav2vec2_arabic!E63</f>
+        <v>0.2</v>
+      </c>
+      <c r="E63" s="6">
         <f>'whisper-base'!H63</f>
         <v>0.96706736087799072</v>
       </c>
-      <c r="E63" s="6">
+      <c r="F63" s="6">
         <f>'whisper-large-v3'!H63</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <f t="shared" si="1"/>
         <v>3.2932519912719727E-2</v>
       </c>
-      <c r="G63">
+      <c r="H63" s="15">
+        <f>wav2vec2_arabic!H64</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I63">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H63">
+      <c r="J63">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K63" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <f>'whisper-base'!E64</f>
         <v>0.33333333333333331</v>
@@ -9738,28 +13466,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="16">
+        <f>wav2vec2_arabic!E64</f>
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="E64" s="6">
         <f>'whisper-base'!H64</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="E64" s="6">
+      <c r="F64" s="6">
         <f>'whisper-large-v3'!H64</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G64">
+      <c r="H64" s="15">
+        <f>wav2vec2_arabic!H65</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I64">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H64">
+      <c r="J64">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K64" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <f>'whisper-base'!E65</f>
         <v>1</v>
@@ -9772,28 +13512,40 @@
         <f t="shared" si="0"/>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="16">
+        <f>wav2vec2_arabic!E65</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="6">
         <f>'whisper-base'!H65</f>
         <v>-1.059324573725462E-2</v>
       </c>
-      <c r="E65" s="6">
+      <c r="F65" s="6">
         <f>'whisper-large-v3'!H65</f>
         <v>0.54131197929382324</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <f t="shared" si="1"/>
         <v>0.55190522503107786</v>
       </c>
-      <c r="G65">
+      <c r="H65" s="15">
+        <f>wav2vec2_arabic!H66</f>
+        <v>0.47954967617988592</v>
+      </c>
+      <c r="I65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H65">
+      <c r="J65">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K65" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <f>'whisper-base'!E66</f>
         <v>0.8</v>
@@ -9806,28 +13558,40 @@
         <f t="shared" si="0"/>
         <v>-0.60000000000000009</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="16">
+        <f>wav2vec2_arabic!E66</f>
+        <v>0.2</v>
+      </c>
+      <c r="E66" s="6">
         <f>'whisper-base'!H66</f>
         <v>6.0340922325849533E-2</v>
       </c>
-      <c r="E66" s="6">
+      <c r="F66" s="6">
         <f>'whisper-large-v3'!H66</f>
         <v>0.34681832790374761</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <f t="shared" si="1"/>
         <v>0.28647740557789808</v>
       </c>
-      <c r="G66">
+      <c r="H66" s="15">
+        <f>wav2vec2_arabic!H67</f>
+        <v>0.85937333106994629</v>
+      </c>
+      <c r="I66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H66">
+      <c r="J66">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K66" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <f>'whisper-base'!E67</f>
         <v>0.8</v>
@@ -9837,31 +13601,43 @@
         <v>0.2</v>
       </c>
       <c r="C67" s="6">
-        <f t="shared" ref="C67:C101" si="4">B67-A67</f>
+        <f t="shared" ref="C67:C101" si="5">B67-A67</f>
         <v>-0.60000000000000009</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="16">
+        <f>wav2vec2_arabic!E67</f>
+        <v>0.4</v>
+      </c>
+      <c r="E67" s="6">
         <f>'whisper-base'!H67</f>
         <v>0.40192386507987982</v>
       </c>
-      <c r="E67" s="6">
+      <c r="F67" s="6">
         <f>'whisper-large-v3'!H67</f>
         <v>0.68062788248062134</v>
       </c>
-      <c r="F67">
-        <f t="shared" ref="F67:F101" si="5">E67-D67</f>
+      <c r="G67">
+        <f t="shared" ref="G67:G101" si="6">F67-E67</f>
         <v>0.27870401740074152</v>
       </c>
-      <c r="G67">
-        <f t="shared" ref="G67:G101" si="6">IF(D67&gt;=0.75, 1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <f t="shared" ref="H67:H101" si="7">IF(E67&gt;=0.75, 1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H67" s="15">
+        <f>wav2vec2_arabic!H68</f>
+        <v>0.64197784662246704</v>
+      </c>
+      <c r="I67">
+        <f t="shared" ref="I67:I101" si="7">IF(E67&gt;=0.75, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J101" si="8">IF(F67&gt;=0.75, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="15">
+        <f t="shared" ref="K67:K101" si="9">IF(H67&gt;=0.75, 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <f>'whisper-base'!E68</f>
         <v>0.3</v>
@@ -9871,31 +13647,43 @@
         <v>0.1</v>
       </c>
       <c r="C68" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.19999999999999998</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="16">
+        <f>wav2vec2_arabic!E68</f>
+        <v>0.6</v>
+      </c>
+      <c r="E68" s="6">
         <f>'whisper-base'!H68</f>
         <v>0.68641412258148193</v>
       </c>
-      <c r="E68" s="6">
+      <c r="F68" s="6">
         <f>'whisper-large-v3'!H68</f>
         <v>0.92965793609619141</v>
       </c>
-      <c r="F68">
-        <f t="shared" si="5"/>
-        <v>0.24324381351470947</v>
-      </c>
       <c r="G68">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H68">
+        <v>0.24324381351470947</v>
+      </c>
+      <c r="H68" s="15">
+        <f>wav2vec2_arabic!H69</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I68">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K68" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <f>'whisper-base'!E69</f>
         <v>1</v>
@@ -9905,31 +13693,43 @@
         <v>0</v>
       </c>
       <c r="C69" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="16">
+        <f>wav2vec2_arabic!E69</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E69" s="6">
         <f>'whisper-base'!H69</f>
         <v>0.13104258477687841</v>
       </c>
-      <c r="E69" s="6">
+      <c r="F69" s="6">
         <f>'whisper-large-v3'!H69</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F69">
-        <f t="shared" si="5"/>
-        <v>0.86895753443241164</v>
-      </c>
       <c r="G69">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H69">
+        <v>0.86895753443241164</v>
+      </c>
+      <c r="H69" s="15">
+        <f>wav2vec2_arabic!H70</f>
+        <v>0.99999994039535522</v>
+      </c>
+      <c r="I69">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K69" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <f>'whisper-base'!E70</f>
         <v>0.75</v>
@@ -9939,31 +13739,43 @@
         <v>0</v>
       </c>
       <c r="C70" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.75</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="16">
+        <f>wav2vec2_arabic!E70</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="6">
         <f>'whisper-base'!H70</f>
         <v>0.98927438259124756</v>
       </c>
-      <c r="E70" s="6">
+      <c r="F70" s="6">
         <f>'whisper-large-v3'!H70</f>
         <v>0.99999994039535522</v>
       </c>
-      <c r="F70">
-        <f t="shared" si="5"/>
-        <v>1.0725557804107666E-2</v>
-      </c>
       <c r="G70">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H70">
+        <v>1.0725557804107666E-2</v>
+      </c>
+      <c r="H70" s="15">
+        <f>wav2vec2_arabic!H71</f>
+        <v>0.79851973056793213</v>
+      </c>
+      <c r="I70">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J70">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K70" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <f>'whisper-base'!E71</f>
         <v>0.16666666666666671</v>
@@ -9973,31 +13785,43 @@
         <v>0</v>
       </c>
       <c r="C71" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.16666666666666671</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="16">
+        <f>wav2vec2_arabic!E71</f>
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="E71" s="6">
         <f>'whisper-base'!H71</f>
         <v>0.79851973056793213</v>
       </c>
-      <c r="E71" s="6">
+      <c r="F71" s="6">
         <f>'whisper-large-v3'!H71</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F71">
-        <f t="shared" si="5"/>
-        <v>0.20148038864135787</v>
-      </c>
       <c r="G71">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H71">
+        <v>0.20148038864135787</v>
+      </c>
+      <c r="H71" s="15">
+        <f>wav2vec2_arabic!H72</f>
+        <v>1</v>
+      </c>
+      <c r="I71">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J71">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K71" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <f>'whisper-base'!E72</f>
         <v>0.5714285714285714</v>
@@ -10007,31 +13831,43 @@
         <v>0.42857142857142849</v>
       </c>
       <c r="C72" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.1428571428571429</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="16">
+        <f>wav2vec2_arabic!E72</f>
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="E72" s="6">
         <f>'whisper-base'!H72</f>
         <v>0.72383338212966919</v>
       </c>
-      <c r="E72" s="6">
+      <c r="F72" s="6">
         <f>'whisper-large-v3'!H72</f>
         <v>0.72383338212966919</v>
       </c>
-      <c r="F72">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="G72">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="15">
+        <f>wav2vec2_arabic!H73</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J72">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <f>'whisper-base'!E73</f>
         <v>1</v>
@@ -10041,31 +13877,43 @@
         <v>0</v>
       </c>
       <c r="C73" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="16">
+        <f>wav2vec2_arabic!E73</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="6">
         <f>'whisper-base'!H73</f>
         <v>1.8437586724758152E-2</v>
       </c>
-      <c r="E73" s="6">
+      <c r="F73" s="6">
         <f>'whisper-large-v3'!H73</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F73">
-        <f t="shared" si="5"/>
-        <v>0.98156253248453185</v>
-      </c>
       <c r="G73">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H73">
+        <v>0.98156253248453185</v>
+      </c>
+      <c r="H73" s="15">
+        <f>wav2vec2_arabic!H74</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I73">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K73" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <f>'whisper-base'!E74</f>
         <v>0</v>
@@ -10075,31 +13923,43 @@
         <v>0</v>
       </c>
       <c r="C74" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D74" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D74" s="16">
+        <f>wav2vec2_arabic!E74</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="6">
         <f>'whisper-base'!H74</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="E74" s="6">
+      <c r="F74" s="6">
         <f>'whisper-large-v3'!H74</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F74">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="G74">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="H74" s="15">
+        <f>wav2vec2_arabic!H75</f>
+        <v>1</v>
+      </c>
+      <c r="I74">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J74">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K74" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <f>'whisper-base'!E75</f>
         <v>1</v>
@@ -10109,31 +13969,43 @@
         <v>0</v>
       </c>
       <c r="C75" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="16">
+        <f>wav2vec2_arabic!E75</f>
+        <v>0.25</v>
+      </c>
+      <c r="E75" s="6">
         <f>'whisper-base'!H75</f>
         <v>0.16181020438671109</v>
       </c>
-      <c r="E75" s="6">
+      <c r="F75" s="6">
         <f>'whisper-large-v3'!H75</f>
         <v>1</v>
-      </c>
-      <c r="F75">
-        <f t="shared" si="5"/>
-        <v>0.83818979561328888</v>
       </c>
       <c r="G75">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H75">
+        <v>0.83818979561328888</v>
+      </c>
+      <c r="H75" s="15">
+        <f>wav2vec2_arabic!H76</f>
+        <v>1</v>
+      </c>
+      <c r="I75">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K75" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <f>'whisper-base'!E76</f>
         <v>1.666666666666667</v>
@@ -10143,31 +14015,43 @@
         <v>0</v>
       </c>
       <c r="C76" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.666666666666667</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D76" s="16">
+        <f>wav2vec2_arabic!E76</f>
+        <v>0</v>
+      </c>
+      <c r="E76" s="6">
         <f>'whisper-base'!H76</f>
         <v>0.1434168815612793</v>
       </c>
-      <c r="E76" s="6">
+      <c r="F76" s="6">
         <f>'whisper-large-v3'!H76</f>
         <v>1</v>
-      </c>
-      <c r="F76">
-        <f t="shared" si="5"/>
-        <v>0.8565831184387207</v>
       </c>
       <c r="G76">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H76">
+        <v>0.8565831184387207</v>
+      </c>
+      <c r="H76" s="15">
+        <f>wav2vec2_arabic!H77</f>
+        <v>1</v>
+      </c>
+      <c r="I76">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K76" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <f>'whisper-base'!E77</f>
         <v>1.25</v>
@@ -10177,31 +14061,43 @@
         <v>0</v>
       </c>
       <c r="C77" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.25</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="16">
+        <f>wav2vec2_arabic!E77</f>
+        <v>0.25</v>
+      </c>
+      <c r="E77" s="6">
         <f>'whisper-base'!H77</f>
         <v>0.2478972673416138</v>
       </c>
-      <c r="E77" s="6">
+      <c r="F77" s="6">
         <f>'whisper-large-v3'!H77</f>
         <v>1</v>
-      </c>
-      <c r="F77">
-        <f t="shared" si="5"/>
-        <v>0.75210273265838623</v>
       </c>
       <c r="G77">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H77">
+        <v>0.75210273265838623</v>
+      </c>
+      <c r="H77" s="15">
+        <f>wav2vec2_arabic!H78</f>
+        <v>0.83503836393356323</v>
+      </c>
+      <c r="I77">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K77" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <f>'whisper-base'!E78</f>
         <v>37</v>
@@ -10211,31 +14107,43 @@
         <v>0.75</v>
       </c>
       <c r="C78" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-36.25</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D78" s="16">
+        <f>wav2vec2_arabic!E78</f>
+        <v>0.75</v>
+      </c>
+      <c r="E78" s="6">
         <f>'whisper-base'!H78</f>
         <v>-5.5422760546207428E-2</v>
       </c>
-      <c r="E78" s="6">
+      <c r="F78" s="6">
         <f>'whisper-large-v3'!H78</f>
         <v>0.51466172933578491</v>
       </c>
-      <c r="F78">
-        <f t="shared" si="5"/>
-        <v>0.57008448988199234</v>
-      </c>
       <c r="G78">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H78">
+        <v>0.57008448988199234</v>
+      </c>
+      <c r="H78" s="15">
+        <f>wav2vec2_arabic!H79</f>
+        <v>0.24166867136955261</v>
+      </c>
+      <c r="I78">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J78">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K78" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <f>'whisper-base'!E79</f>
         <v>1</v>
@@ -10245,31 +14153,43 @@
         <v>1</v>
       </c>
       <c r="C79" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D79" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D79" s="16">
+        <f>wav2vec2_arabic!E79</f>
+        <v>1</v>
+      </c>
+      <c r="E79" s="6">
         <f>'whisper-base'!H79</f>
         <v>2.3152250796556469E-2</v>
       </c>
-      <c r="E79" s="6">
+      <c r="F79" s="6">
         <f>'whisper-large-v3'!H79</f>
         <v>7.7558375895023346E-2</v>
       </c>
-      <c r="F79">
-        <f t="shared" si="5"/>
-        <v>5.4406125098466873E-2</v>
-      </c>
       <c r="G79">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H79">
+        <v>5.4406125098466873E-2</v>
+      </c>
+      <c r="H79" s="15">
+        <f>wav2vec2_arabic!H80</f>
+        <v>0.26109665632247919</v>
+      </c>
+      <c r="I79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <f>'whisper-base'!E80</f>
         <v>1</v>
@@ -10279,31 +14199,43 @@
         <v>0</v>
       </c>
       <c r="C80" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D80" s="16">
+        <f>wav2vec2_arabic!E80</f>
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="6">
         <f>'whisper-base'!H80</f>
         <v>0.1914719492197037</v>
       </c>
-      <c r="E80" s="6">
+      <c r="F80" s="6">
         <f>'whisper-large-v3'!H80</f>
         <v>0.99999994039535522</v>
       </c>
-      <c r="F80">
-        <f t="shared" si="5"/>
-        <v>0.80852799117565155</v>
-      </c>
       <c r="G80">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H80">
+        <v>0.80852799117565155</v>
+      </c>
+      <c r="H80" s="15">
+        <f>wav2vec2_arabic!H81</f>
+        <v>0.53660047054290771</v>
+      </c>
+      <c r="I80">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K80" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <f>'whisper-base'!E81</f>
         <v>1</v>
@@ -10313,31 +14245,43 @@
         <v>1</v>
       </c>
       <c r="C81" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D81" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D81" s="16">
+        <f>wav2vec2_arabic!E81</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E81" s="6">
         <f>'whisper-base'!H81</f>
         <v>0.25752788782119751</v>
       </c>
-      <c r="E81" s="6">
+      <c r="F81" s="6">
         <f>'whisper-large-v3'!H81</f>
         <v>0.1288997828960419</v>
       </c>
-      <c r="F81">
-        <f t="shared" si="5"/>
-        <v>-0.12862810492515561</v>
-      </c>
       <c r="G81">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H81">
+        <v>-0.12862810492515561</v>
+      </c>
+      <c r="H81" s="15">
+        <f>wav2vec2_arabic!H82</f>
+        <v>1</v>
+      </c>
+      <c r="I81">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J81">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K81" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <f>'whisper-base'!E82</f>
         <v>0.66666666666666663</v>
@@ -10347,31 +14291,43 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C82" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D82" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D82" s="16">
+        <f>wav2vec2_arabic!E82</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E82" s="6">
         <f>'whisper-base'!H82</f>
         <v>1</v>
       </c>
-      <c r="E82" s="6">
+      <c r="F82" s="6">
         <f>'whisper-large-v3'!H82</f>
         <v>1</v>
-      </c>
-      <c r="F82">
-        <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="G82">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="H82" s="15">
+        <f>wav2vec2_arabic!H83</f>
+        <v>1</v>
+      </c>
+      <c r="I82">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J82">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K82" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <f>'whisper-base'!E83</f>
         <v>0.8571428571428571</v>
@@ -10381,31 +14337,43 @@
         <v>0.14285714285714279</v>
       </c>
       <c r="C83" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.7142857142857143</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="16">
+        <f>wav2vec2_arabic!E83</f>
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="E83" s="6">
         <f>'whisper-base'!H83</f>
         <v>0.36957472562789923</v>
       </c>
-      <c r="E83" s="6">
+      <c r="F83" s="6">
         <f>'whisper-large-v3'!H83</f>
         <v>0.45813319087028498</v>
       </c>
-      <c r="F83">
-        <f t="shared" si="5"/>
-        <v>8.8558465242385753E-2</v>
-      </c>
       <c r="G83">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H83">
+        <v>8.8558465242385753E-2</v>
+      </c>
+      <c r="H83" s="15">
+        <f>wav2vec2_arabic!H84</f>
+        <v>0.98480850458145142</v>
+      </c>
+      <c r="I83">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J83">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K83" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <f>'whisper-base'!E84</f>
         <v>0</v>
@@ -10415,31 +14383,43 @@
         <v>0.25</v>
       </c>
       <c r="C84" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D84" s="16">
+        <f>wav2vec2_arabic!E84</f>
+        <v>1.25</v>
+      </c>
+      <c r="E84" s="6">
         <f>'whisper-base'!H84</f>
         <v>0.9999997615814209</v>
       </c>
-      <c r="E84" s="6">
+      <c r="F84" s="6">
         <f>'whisper-large-v3'!H84</f>
         <v>0.9999997615814209</v>
       </c>
-      <c r="F84">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="G84">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="H84" s="15">
+        <f>wav2vec2_arabic!H85</f>
+        <v>1</v>
+      </c>
+      <c r="I84">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J84">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K84" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <f>'whisper-base'!E85</f>
         <v>0.66666666666666663</v>
@@ -10449,31 +14429,43 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C85" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="16">
+        <f>wav2vec2_arabic!E85</f>
+        <v>0</v>
+      </c>
+      <c r="E85" s="6">
         <f>'whisper-base'!H85</f>
         <v>0.62865197658538818</v>
       </c>
-      <c r="E85" s="6">
+      <c r="F85" s="6">
         <f>'whisper-large-v3'!H85</f>
         <v>1</v>
-      </c>
-      <c r="F85">
-        <f t="shared" si="5"/>
-        <v>0.37134802341461182</v>
       </c>
       <c r="G85">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H85">
+        <v>0.37134802341461182</v>
+      </c>
+      <c r="H85" s="15">
+        <f>wav2vec2_arabic!H86</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I85">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K85" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <f>'whisper-base'!E86</f>
         <v>0.33333333333333331</v>
@@ -10483,31 +14475,43 @@
         <v>0</v>
       </c>
       <c r="C86" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="16">
+        <f>wav2vec2_arabic!E86</f>
+        <v>0</v>
+      </c>
+      <c r="E86" s="6">
         <f>'whisper-base'!H86</f>
         <v>0.64542430639266968</v>
       </c>
-      <c r="E86" s="6">
+      <c r="F86" s="6">
         <f>'whisper-large-v3'!H86</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F86">
-        <f t="shared" si="5"/>
-        <v>0.35457581281662032</v>
-      </c>
       <c r="G86">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H86">
+        <v>0.35457581281662032</v>
+      </c>
+      <c r="H86" s="15">
+        <f>wav2vec2_arabic!H87</f>
+        <v>1</v>
+      </c>
+      <c r="I86">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K86" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <f>'whisper-base'!E87</f>
         <v>1</v>
@@ -10517,31 +14521,43 @@
         <v>0</v>
       </c>
       <c r="C87" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="16">
+        <f>wav2vec2_arabic!E87</f>
+        <v>0</v>
+      </c>
+      <c r="E87" s="6">
         <f>'whisper-base'!H87</f>
         <v>0.37523728609085077</v>
       </c>
-      <c r="E87" s="6">
+      <c r="F87" s="6">
         <f>'whisper-large-v3'!H87</f>
         <v>1</v>
-      </c>
-      <c r="F87">
-        <f t="shared" si="5"/>
-        <v>0.62476271390914917</v>
       </c>
       <c r="G87">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H87">
+        <v>0.62476271390914917</v>
+      </c>
+      <c r="H87" s="15">
+        <f>wav2vec2_arabic!H88</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I87">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K87" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <f>'whisper-base'!E88</f>
         <v>0.25</v>
@@ -10551,31 +14567,43 @@
         <v>0.25</v>
       </c>
       <c r="C88" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D88" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="16">
+        <f>wav2vec2_arabic!E88</f>
+        <v>0.25</v>
+      </c>
+      <c r="E88" s="6">
         <f>'whisper-base'!H88</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="E88" s="6">
+      <c r="F88" s="6">
         <f>'whisper-large-v3'!H88</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F88">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="G88">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="H88" s="15">
+        <f>wav2vec2_arabic!H89</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I88">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J88">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K88" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <f>'whisper-base'!E89</f>
         <v>0.2</v>
@@ -10585,31 +14613,43 @@
         <v>0</v>
       </c>
       <c r="C89" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.2</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="16">
+        <f>wav2vec2_arabic!E89</f>
+        <v>0</v>
+      </c>
+      <c r="E89" s="6">
         <f>'whisper-base'!H89</f>
         <v>0.72023451328277588</v>
       </c>
-      <c r="E89" s="6">
+      <c r="F89" s="6">
         <f>'whisper-large-v3'!H89</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F89">
-        <f t="shared" si="5"/>
-        <v>0.27976572513580322</v>
-      </c>
       <c r="G89">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H89">
+        <v>0.27976572513580322</v>
+      </c>
+      <c r="H89" s="15">
+        <f>wav2vec2_arabic!H90</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I89">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K89" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <f>'whisper-base'!E90</f>
         <v>0.8571428571428571</v>
@@ -10619,31 +14659,43 @@
         <v>0</v>
       </c>
       <c r="C90" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.8571428571428571</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="16">
+        <f>wav2vec2_arabic!E90</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="6">
         <f>'whisper-base'!H90</f>
         <v>4.7507055103778839E-2</v>
       </c>
-      <c r="E90" s="6">
+      <c r="F90" s="6">
         <f>'whisper-large-v3'!H90</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F90">
-        <f t="shared" si="5"/>
-        <v>0.95249318331480026</v>
-      </c>
       <c r="G90">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H90">
+        <v>0.95249318331480026</v>
+      </c>
+      <c r="H90" s="15">
+        <f>wav2vec2_arabic!H91</f>
+        <v>0.9999997615814209</v>
+      </c>
+      <c r="I90">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K90" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <f>'whisper-base'!E91</f>
         <v>0.8</v>
@@ -10653,31 +14705,43 @@
         <v>0</v>
       </c>
       <c r="C91" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.8</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="16">
+        <f>wav2vec2_arabic!E91</f>
+        <v>0</v>
+      </c>
+      <c r="E91" s="6">
         <f>'whisper-base'!H91</f>
         <v>0.27129131555557251</v>
       </c>
-      <c r="E91" s="6">
+      <c r="F91" s="6">
         <f>'whisper-large-v3'!H91</f>
         <v>0.9999997615814209</v>
       </c>
-      <c r="F91">
-        <f t="shared" si="5"/>
-        <v>0.72870844602584839</v>
-      </c>
       <c r="G91">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H91">
+        <v>0.72870844602584839</v>
+      </c>
+      <c r="H91" s="15">
+        <f>wav2vec2_arabic!H92</f>
+        <v>0.67245244979858398</v>
+      </c>
+      <c r="I91">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K91" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <f>'whisper-base'!E92</f>
         <v>0.8</v>
@@ -10687,31 +14751,43 @@
         <v>0.4</v>
       </c>
       <c r="C92" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.4</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D92" s="16">
+        <f>wav2vec2_arabic!E92</f>
+        <v>0.6</v>
+      </c>
+      <c r="E92" s="6">
         <f>'whisper-base'!H92</f>
         <v>0.38401356339454651</v>
       </c>
-      <c r="E92" s="6">
+      <c r="F92" s="6">
         <f>'whisper-large-v3'!H92</f>
         <v>0.89645522832870483</v>
       </c>
-      <c r="F92">
-        <f t="shared" si="5"/>
-        <v>0.51244166493415833</v>
-      </c>
       <c r="G92">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H92">
+        <v>0.51244166493415833</v>
+      </c>
+      <c r="H92" s="15">
+        <f>wav2vec2_arabic!H93</f>
+        <v>0.99999988079071045</v>
+      </c>
+      <c r="I92">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K92" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <f>'whisper-base'!E93</f>
         <v>0.5</v>
@@ -10721,31 +14797,43 @@
         <v>0</v>
       </c>
       <c r="C93" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.5</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D93" s="16">
+        <f>wav2vec2_arabic!E93</f>
+        <v>0</v>
+      </c>
+      <c r="E93" s="6">
         <f>'whisper-base'!H93</f>
         <v>0.83618956804275513</v>
       </c>
-      <c r="E93" s="6">
+      <c r="F93" s="6">
         <f>'whisper-large-v3'!H93</f>
         <v>0.99999988079071045</v>
       </c>
-      <c r="F93">
-        <f t="shared" si="5"/>
-        <v>0.16381031274795532</v>
-      </c>
       <c r="G93">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H93">
+        <v>0.16381031274795532</v>
+      </c>
+      <c r="H93" s="15">
+        <f>wav2vec2_arabic!H94</f>
+        <v>0.86750668287277222</v>
+      </c>
+      <c r="I93">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J93">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K93" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <f>'whisper-base'!E94</f>
         <v>1</v>
@@ -10755,31 +14843,43 @@
         <v>0</v>
       </c>
       <c r="C94" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="D94" s="6">
+      <c r="D94" s="16">
+        <f>wav2vec2_arabic!E94</f>
+        <v>1</v>
+      </c>
+      <c r="E94" s="6">
         <f>'whisper-base'!H94</f>
         <v>0.47174209356307978</v>
       </c>
-      <c r="E94" s="6">
+      <c r="F94" s="6">
         <f>'whisper-large-v3'!H94</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F94">
-        <f t="shared" si="5"/>
-        <v>0.52825802564621016</v>
-      </c>
       <c r="G94">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H94">
+        <v>0.52825802564621016</v>
+      </c>
+      <c r="H94" s="15">
+        <f>wav2vec2_arabic!H95</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I94">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K94" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <f>'whisper-base'!E95</f>
         <v>0.625</v>
@@ -10789,31 +14889,43 @@
         <v>0.125</v>
       </c>
       <c r="C95" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.5</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D95" s="16">
+        <f>wav2vec2_arabic!E95</f>
+        <v>0.25</v>
+      </c>
+      <c r="E95" s="6">
         <f>'whisper-base'!H95</f>
         <v>0.25295090675353998</v>
       </c>
-      <c r="E95" s="6">
+      <c r="F95" s="6">
         <f>'whisper-large-v3'!H95</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F95">
-        <f t="shared" si="5"/>
-        <v>0.74704921245574996</v>
-      </c>
       <c r="G95">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H95">
+        <v>0.74704921245574996</v>
+      </c>
+      <c r="H95" s="15">
+        <f>wav2vec2_arabic!H96</f>
+        <v>0.46461623907089228</v>
+      </c>
+      <c r="I95">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K95" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <f>'whisper-base'!E96</f>
         <v>0.66666666666666663</v>
@@ -10823,31 +14935,43 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C96" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D96" s="6">
+      <c r="D96" s="16">
+        <f>wav2vec2_arabic!E96</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E96" s="6">
         <f>'whisper-base'!H96</f>
         <v>0.43852174282073969</v>
       </c>
-      <c r="E96" s="6">
+      <c r="F96" s="6">
         <f>'whisper-large-v3'!H96</f>
         <v>1</v>
-      </c>
-      <c r="F96">
-        <f t="shared" si="5"/>
-        <v>0.56147825717926025</v>
       </c>
       <c r="G96">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H96">
+        <v>0.56147825717926025</v>
+      </c>
+      <c r="H96" s="15">
+        <f>wav2vec2_arabic!H97</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I96">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K96" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <f>'whisper-base'!E97</f>
         <v>1</v>
@@ -10857,31 +14981,43 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C97" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.33333333333333337</v>
       </c>
-      <c r="D97" s="6">
+      <c r="D97" s="16">
+        <f>wav2vec2_arabic!E97</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="6">
         <f>'whisper-base'!H97</f>
         <v>0.32894977927207952</v>
       </c>
-      <c r="E97" s="6">
+      <c r="F97" s="6">
         <f>'whisper-large-v3'!H97</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F97">
-        <f t="shared" si="5"/>
-        <v>0.67105045914649963</v>
-      </c>
       <c r="G97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H97">
+        <v>0.67105045914649963</v>
+      </c>
+      <c r="H97" s="15">
+        <f>wav2vec2_arabic!H98</f>
+        <v>1</v>
+      </c>
+      <c r="I97">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K97" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <f>'whisper-base'!E98</f>
         <v>0.5</v>
@@ -10891,31 +15027,43 @@
         <v>0</v>
       </c>
       <c r="C98" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.5</v>
       </c>
-      <c r="D98" s="6">
+      <c r="D98" s="16">
+        <f>wav2vec2_arabic!E98</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="6">
         <f>'whisper-base'!H98</f>
         <v>0.52061766386032104</v>
       </c>
-      <c r="E98" s="6">
+      <c r="F98" s="6">
         <f>'whisper-large-v3'!H98</f>
         <v>1</v>
-      </c>
-      <c r="F98">
-        <f t="shared" si="5"/>
-        <v>0.47938233613967896</v>
       </c>
       <c r="G98">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H98">
+        <v>0.47938233613967896</v>
+      </c>
+      <c r="H98" s="15">
+        <f>wav2vec2_arabic!H99</f>
+        <v>1.00000011920929</v>
+      </c>
+      <c r="I98">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K98" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <f>'whisper-base'!E99</f>
         <v>0</v>
@@ -10925,31 +15073,43 @@
         <v>0</v>
       </c>
       <c r="C99" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D99" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D99" s="16">
+        <f>wav2vec2_arabic!E99</f>
+        <v>0</v>
+      </c>
+      <c r="E99" s="6">
         <f>'whisper-base'!H99</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="E99" s="6">
+      <c r="F99" s="6">
         <f>'whisper-large-v3'!H99</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="F99">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="G99">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="H99" s="15">
+        <f>wav2vec2_arabic!H100</f>
+        <v>1</v>
+      </c>
+      <c r="I99">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J99">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K99" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <f>'whisper-base'!E100</f>
         <v>0.75</v>
@@ -10959,31 +15119,43 @@
         <v>0.25</v>
       </c>
       <c r="C100" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.5</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="16">
+        <f>wav2vec2_arabic!E100</f>
+        <v>0.25</v>
+      </c>
+      <c r="E100" s="6">
         <f>'whisper-base'!H100</f>
         <v>0.68903940916061401</v>
       </c>
-      <c r="E100" s="6">
+      <c r="F100" s="6">
         <f>'whisper-large-v3'!H100</f>
         <v>1</v>
-      </c>
-      <c r="F100">
-        <f t="shared" si="5"/>
-        <v>0.31096059083938599</v>
       </c>
       <c r="G100">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H100">
+        <v>0.31096059083938599</v>
+      </c>
+      <c r="H100" s="15">
+        <f>wav2vec2_arabic!H101</f>
+        <v>1.0000002384185791</v>
+      </c>
+      <c r="I100">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K100" s="15">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <f>'whisper-base'!E101</f>
         <v>0.33333333333333331</v>
@@ -10993,28 +15165,40 @@
         <v>0</v>
       </c>
       <c r="C101" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="16">
+        <f>wav2vec2_arabic!E101</f>
+        <v>0</v>
+      </c>
+      <c r="E101" s="6">
         <f>'whisper-base'!H101</f>
         <v>1.00000011920929</v>
       </c>
-      <c r="E101" s="6">
+      <c r="F101" s="6">
         <f>'whisper-large-v3'!H101</f>
         <v>1.0000002384185791</v>
       </c>
-      <c r="F101">
-        <f t="shared" si="5"/>
-        <v>1.1920928910669204E-7</v>
-      </c>
       <c r="G101">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H101">
+        <v>1.1920928910669204E-7</v>
+      </c>
+      <c r="H101" s="15">
+        <f>wav2vec2_arabic!H102</f>
+        <v>0</v>
+      </c>
+      <c r="I101">
         <f t="shared" si="7"/>
         <v>1</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K101" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11036,7 +15220,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576 G1:H1">
+  <conditionalFormatting sqref="G1:G1048576 I1:K1">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
